--- a/tests/fixtures/super_fund_level_sample.xlsx
+++ b/tests/fixtures/super_fund_level_sample.xlsx
@@ -11085,7 +11085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U80"/>
+  <dimension ref="A1:U81"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col width="13.140625" customWidth="1" min="1" max="1"/>
@@ -11119,7 +11119,11 @@
       <c r="U2" s="111" t="n"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="103" t="n"/>
+      <c r="A3" s="103" t="inlineStr">
+        <is>
+          <t>Member account status</t>
+        </is>
+      </c>
       <c r="B3" s="103" t="n"/>
       <c r="C3" s="103" t="n"/>
       <c r="D3" s="103" t="n"/>
@@ -11186,311 +11190,335 @@
       </c>
     </row>
     <row r="4" ht="105" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B4" s="26" t="inlineStr">
-        <is>
-          <t>Fund name</t>
-        </is>
-      </c>
-      <c r="C4" s="26" t="inlineStr">
-        <is>
-          <t>ABN</t>
-        </is>
-      </c>
-      <c r="D4" s="26" t="inlineStr">
-        <is>
-          <t>RSE Regulatory classification</t>
-        </is>
-      </c>
-      <c r="E4" s="26" t="inlineStr">
-        <is>
-          <t>Fund type</t>
-        </is>
-      </c>
-      <c r="F4" s="26" t="inlineStr">
-        <is>
-          <t>RSE Membership base</t>
-        </is>
-      </c>
-      <c r="G4" s="26" t="inlineStr">
-        <is>
-          <t>Fund's RSE licensee</t>
-        </is>
-      </c>
-      <c r="H4" s="26" t="inlineStr">
-        <is>
-          <t>RSE licensee ownership type</t>
-        </is>
-      </c>
-      <c r="I4" s="26" t="inlineStr">
-        <is>
-          <t>RSE licensee profit status</t>
-        </is>
-      </c>
-      <c r="J4" s="26" t="inlineStr">
-        <is>
-          <t>RSE licensee board structure</t>
-        </is>
-      </c>
-      <c r="K4" s="27" t="inlineStr">
-        <is>
-          <t>Total number of member accounts at the end of period</t>
-        </is>
-      </c>
-      <c r="L4" s="27" t="inlineStr">
-        <is>
-          <t>Total members' benefits at end of period</t>
-        </is>
-      </c>
-      <c r="M4" s="27" t="inlineStr">
-        <is>
-          <t>Median benefit bracket</t>
-        </is>
-      </c>
-      <c r="N4" s="27" t="inlineStr">
-        <is>
-          <t>Estimated median account balance</t>
-        </is>
-      </c>
-      <c r="O4" s="27" t="inlineStr">
-        <is>
-          <t>Median member age</t>
-        </is>
-      </c>
-      <c r="P4" s="27" t="inlineStr">
-        <is>
-          <t>Number of active member accounts</t>
-        </is>
-      </c>
-      <c r="Q4" s="27" t="inlineStr">
-        <is>
-          <t>Number of inactive member accounts</t>
-        </is>
-      </c>
-      <c r="R4" s="27" t="inlineStr">
-        <is>
-          <t>Members' benefits of active member accounts</t>
-        </is>
-      </c>
-      <c r="S4" s="27" t="inlineStr">
-        <is>
-          <t>Members' benefits of inactive member accounts</t>
-        </is>
-      </c>
-      <c r="T4" s="27" t="inlineStr">
-        <is>
-          <t>Average member account balance of active member accounts</t>
-        </is>
-      </c>
-      <c r="U4" s="20" t="inlineStr">
-        <is>
-          <t>Average member account balance of inactive member accounts</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>U</t>
         </is>
       </c>
     </row>
     <row r="5" ht="70.34999999999999" customHeight="1">
-      <c r="A5" s="28" t="n"/>
-      <c r="B5" s="28" t="n"/>
-      <c r="C5" s="28" t="n"/>
-      <c r="D5" s="29" t="n"/>
-      <c r="E5" s="29" t="n"/>
-      <c r="F5" s="30" t="n"/>
-      <c r="G5" s="29" t="n"/>
-      <c r="H5" s="29" t="n"/>
-      <c r="I5" s="29" t="n"/>
-      <c r="J5" s="29" t="n"/>
-      <c r="K5" s="31" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>Fund name</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>ABN</t>
+        </is>
+      </c>
+      <c r="D5" s="26" t="inlineStr">
+        <is>
+          <t>RSE Regulatory classification</t>
+        </is>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t>Fund type</t>
+        </is>
+      </c>
+      <c r="F5" s="26" t="inlineStr">
+        <is>
+          <t>RSE Membership base</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="inlineStr">
+        <is>
+          <t>Fund's RSE licensee</t>
+        </is>
+      </c>
+      <c r="H5" s="26" t="inlineStr">
+        <is>
+          <t>RSE licensee ownership type</t>
+        </is>
+      </c>
+      <c r="I5" s="26" t="inlineStr">
+        <is>
+          <t>RSE licensee profit status</t>
+        </is>
+      </c>
+      <c r="J5" s="26" t="inlineStr">
+        <is>
+          <t>RSE licensee board structure</t>
+        </is>
+      </c>
+      <c r="K5" s="27" t="inlineStr">
+        <is>
+          <t>Total number of member accounts at the end of period</t>
+        </is>
+      </c>
+      <c r="L5" s="27" t="inlineStr">
+        <is>
+          <t>Total members' benefits at end of period</t>
+        </is>
+      </c>
+      <c r="M5" s="27" t="inlineStr">
+        <is>
+          <t>Median benefit bracket</t>
+        </is>
+      </c>
+      <c r="N5" s="27" t="inlineStr">
+        <is>
+          <t>Estimated median account balance</t>
+        </is>
+      </c>
+      <c r="O5" s="27" t="inlineStr">
+        <is>
+          <t>Median member age</t>
+        </is>
+      </c>
+      <c r="P5" s="27" t="inlineStr">
+        <is>
+          <t>Number of active member accounts</t>
+        </is>
+      </c>
+      <c r="Q5" s="27" t="inlineStr">
+        <is>
+          <t>Number of inactive member accounts</t>
+        </is>
+      </c>
+      <c r="R5" s="27" t="inlineStr">
+        <is>
+          <t>Members' benefits of active member accounts</t>
+        </is>
+      </c>
+      <c r="S5" s="27" t="inlineStr">
+        <is>
+          <t>Members' benefits of inactive member accounts</t>
+        </is>
+      </c>
+      <c r="T5" s="27" t="inlineStr">
+        <is>
+          <t>Average member account balance of active member accounts</t>
+        </is>
+      </c>
+      <c r="U5" s="20" t="inlineStr">
+        <is>
+          <t>Average member account balance of inactive member accounts</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="28" t="n"/>
+      <c r="B6" s="28" t="n"/>
+      <c r="C6" s="28" t="n"/>
+      <c r="D6" s="29" t="n"/>
+      <c r="E6" s="29" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="29" t="n"/>
+      <c r="H6" s="29" t="n"/>
+      <c r="I6" s="29" t="n"/>
+      <c r="J6" s="29" t="n"/>
+      <c r="K6" s="31" t="inlineStr">
         <is>
           <t>SRF 611 Table 1 Column 5</t>
         </is>
       </c>
-      <c r="L5" s="32" t="inlineStr">
+      <c r="L6" s="32" t="inlineStr">
         <is>
           <t>SRF 611 Table 1 Column 6</t>
         </is>
       </c>
-      <c r="M5" s="31" t="inlineStr">
+      <c r="M6" s="31" t="inlineStr">
         <is>
           <t>CS3_010</t>
         </is>
       </c>
-      <c r="N5" s="31" t="inlineStr">
+      <c r="N6" s="31" t="inlineStr">
         <is>
           <t>CS5_001</t>
         </is>
       </c>
-      <c r="O5" s="31" t="inlineStr">
+      <c r="O6" s="31" t="inlineStr">
         <is>
           <t>CS3_018</t>
         </is>
       </c>
-      <c r="P5" s="31" t="inlineStr">
+      <c r="P6" s="31" t="inlineStr">
         <is>
           <t>SRF 611.0
 Column 4 &amp; 5</t>
         </is>
       </c>
-      <c r="Q5" s="31" t="inlineStr">
+      <c r="Q6" s="31" t="inlineStr">
         <is>
           <t>SRF 611.0
 Column 4 &amp; 5</t>
         </is>
       </c>
-      <c r="R5" s="32" t="inlineStr">
+      <c r="R6" s="32" t="inlineStr">
         <is>
           <t>SRF 611.0
 Column 4 &amp; 6</t>
         </is>
       </c>
-      <c r="S5" s="32" t="inlineStr">
+      <c r="S6" s="32" t="inlineStr">
         <is>
           <t>SRF 611.0
 Column 4 &amp; 6</t>
         </is>
       </c>
-      <c r="T5" s="32" t="inlineStr">
+      <c r="T6" s="32" t="inlineStr">
         <is>
           <t>L / J</t>
         </is>
       </c>
-      <c r="U5" s="32" t="inlineStr">
+      <c r="U6" s="32" t="inlineStr">
         <is>
           <t>M / K</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="33" t="n"/>
-      <c r="B6" s="33" t="n"/>
-      <c r="C6" s="33" t="n"/>
-      <c r="D6" s="34" t="n"/>
-      <c r="E6" s="34" t="n"/>
-      <c r="F6" s="35" t="n"/>
-      <c r="G6" s="34" t="n"/>
-      <c r="H6" s="34" t="n"/>
-      <c r="I6" s="34" t="n"/>
-      <c r="J6" s="34" t="n"/>
-      <c r="K6" s="97" t="n"/>
-      <c r="L6" s="36" t="inlineStr">
-        <is>
-          <t>($'000)</t>
-        </is>
-      </c>
-      <c r="M6" s="36" t="n"/>
-      <c r="N6" s="37" t="inlineStr">
-        <is>
-          <t>($)</t>
-        </is>
-      </c>
-      <c r="O6" s="37" t="n"/>
-      <c r="P6" s="37" t="n"/>
-      <c r="Q6" s="37" t="n"/>
-      <c r="R6" s="36" t="inlineStr">
-        <is>
-          <t>($'000)</t>
-        </is>
-      </c>
-      <c r="S6" s="36" t="inlineStr">
-        <is>
-          <t>($'000)</t>
-        </is>
-      </c>
-      <c r="T6" s="36" t="inlineStr">
-        <is>
-          <t>($'000)</t>
-        </is>
-      </c>
-      <c r="U6" s="21" t="inlineStr">
-        <is>
-          <t>($'000)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="13.5" customFormat="1" customHeight="1" s="39">
-      <c r="A7" s="38" t="n">
-        <v>46022</v>
-      </c>
-      <c r="B7" s="39" t="inlineStr">
-        <is>
-          <t>AMG Super</t>
-        </is>
-      </c>
-      <c r="C7" s="39" t="n">
-        <v>30099320583</v>
-      </c>
-      <c r="D7" s="39" t="inlineStr">
-        <is>
-          <t>public offer</t>
-        </is>
-      </c>
-      <c r="E7" s="39" t="inlineStr">
-        <is>
-          <t>RETAIL</t>
-        </is>
-      </c>
-      <c r="F7" s="39" t="inlineStr">
-        <is>
-          <t>General base</t>
-        </is>
-      </c>
-      <c r="G7" s="39" t="inlineStr">
-        <is>
-          <t>Equity Trustees Superannuation Limited</t>
-        </is>
-      </c>
-      <c r="H7" s="39" t="inlineStr">
-        <is>
-          <t>Financial services corporation ownership</t>
-        </is>
-      </c>
-      <c r="I7" s="39" t="inlineStr">
-        <is>
-          <t>For profit status</t>
-        </is>
-      </c>
-      <c r="J7" s="39" t="inlineStr">
-        <is>
-          <t>Non equal representation</t>
-        </is>
-      </c>
-      <c r="K7" s="40" t="n">
-        <v>31280</v>
-      </c>
-      <c r="L7" s="40" t="n">
-        <v>2829015</v>
-      </c>
-      <c r="M7" s="40" t="inlineStr">
-        <is>
-          <t>$25,000 to $39,999</t>
-        </is>
-      </c>
-      <c r="N7" s="40" t="n">
-        <v>27601</v>
-      </c>
-      <c r="O7" s="40" t="n">
-        <v>40</v>
-      </c>
-      <c r="P7" s="40" t="n">
-        <v>20020</v>
-      </c>
-      <c r="Q7" s="40" t="n">
-        <v>11260</v>
-      </c>
-      <c r="R7" s="40" t="n">
-        <v>2289286</v>
-      </c>
-      <c r="S7" s="40" t="n">
-        <v>539729</v>
-      </c>
-      <c r="T7" s="40" t="n">
-        <v>114.4</v>
-      </c>
-      <c r="U7" s="40" t="n">
-        <v>47.9</v>
+      <c r="A7" s="33" t="n"/>
+      <c r="B7" s="33" t="n"/>
+      <c r="C7" s="33" t="n"/>
+      <c r="D7" s="34" t="n"/>
+      <c r="E7" s="34" t="n"/>
+      <c r="F7" s="35" t="n"/>
+      <c r="G7" s="34" t="n"/>
+      <c r="H7" s="34" t="n"/>
+      <c r="I7" s="34" t="n"/>
+      <c r="J7" s="34" t="n"/>
+      <c r="K7" s="97" t="n"/>
+      <c r="L7" s="36" t="inlineStr">
+        <is>
+          <t>($'000)</t>
+        </is>
+      </c>
+      <c r="M7" s="36" t="n"/>
+      <c r="N7" s="37" t="inlineStr">
+        <is>
+          <t>($)</t>
+        </is>
+      </c>
+      <c r="O7" s="37" t="n"/>
+      <c r="P7" s="37" t="n"/>
+      <c r="Q7" s="37" t="n"/>
+      <c r="R7" s="36" t="inlineStr">
+        <is>
+          <t>($'000)</t>
+        </is>
+      </c>
+      <c r="S7" s="36" t="inlineStr">
+        <is>
+          <t>($'000)</t>
+        </is>
+      </c>
+      <c r="T7" s="36" t="inlineStr">
+        <is>
+          <t>($'000)</t>
+        </is>
+      </c>
+      <c r="U7" s="21" t="inlineStr">
+        <is>
+          <t>($'000)</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -11499,11 +11527,11 @@
       </c>
       <c r="B8" s="39" t="inlineStr">
         <is>
-          <t>AMP Super Fund</t>
+          <t>AMG Super</t>
         </is>
       </c>
       <c r="C8" s="39" t="n">
-        <v>78421957449</v>
+        <v>30099320583</v>
       </c>
       <c r="D8" s="39" t="inlineStr">
         <is>
@@ -11522,7 +11550,7 @@
       </c>
       <c r="G8" s="39" t="inlineStr">
         <is>
-          <t>N. M. Superannuation Proprietary Limited</t>
+          <t>Equity Trustees Superannuation Limited</t>
         </is>
       </c>
       <c r="H8" s="39" t="inlineStr">
@@ -11541,39 +11569,39 @@
         </is>
       </c>
       <c r="K8" s="40" t="n">
-        <v>573790</v>
+        <v>31280</v>
       </c>
       <c r="L8" s="40" t="n">
-        <v>59958801</v>
+        <v>2829015</v>
       </c>
       <c r="M8" s="40" t="inlineStr">
         <is>
-          <t>$40,000 to $59,999</t>
+          <t>$25,000 to $39,999</t>
         </is>
       </c>
       <c r="N8" s="40" t="n">
-        <v>48067</v>
+        <v>27601</v>
       </c>
       <c r="O8" s="40" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="P8" s="40" t="n">
-        <v>346880</v>
+        <v>20020</v>
       </c>
       <c r="Q8" s="40" t="n">
-        <v>226910</v>
+        <v>11260</v>
       </c>
       <c r="R8" s="40" t="n">
-        <v>42674891</v>
+        <v>2289286</v>
       </c>
       <c r="S8" s="40" t="n">
-        <v>17283909</v>
+        <v>539729</v>
       </c>
       <c r="T8" s="40" t="n">
-        <v>123</v>
+        <v>114.4</v>
       </c>
       <c r="U8" s="40" t="n">
-        <v>76.2</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="9" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -11582,81 +11610,81 @@
       </c>
       <c r="B9" s="39" t="inlineStr">
         <is>
-          <t>ANZ Australian Staff Superannuation Scheme</t>
+          <t>AMP Super Fund</t>
         </is>
       </c>
       <c r="C9" s="39" t="n">
-        <v>83810127567</v>
+        <v>78421957449</v>
       </c>
       <c r="D9" s="39" t="inlineStr">
         <is>
-          <t>non-public offer</t>
+          <t>public offer</t>
         </is>
       </c>
       <c r="E9" s="39" t="inlineStr">
         <is>
-          <t>CORPORATE</t>
+          <t>RETAIL</t>
         </is>
       </c>
       <c r="F9" s="39" t="inlineStr">
         <is>
-          <t>Corporate base</t>
+          <t>General base</t>
         </is>
       </c>
       <c r="G9" s="39" t="inlineStr">
         <is>
-          <t>ANZ Staff Superannuation (Australia) Pty. Limited</t>
+          <t>N. M. Superannuation Proprietary Limited</t>
         </is>
       </c>
       <c r="H9" s="39" t="inlineStr">
         <is>
-          <t>Employer sponsor (non-public sector) ownership</t>
+          <t>Financial services corporation ownership</t>
         </is>
       </c>
       <c r="I9" s="39" t="inlineStr">
         <is>
-          <t>Not for profit status</t>
+          <t>For profit status</t>
         </is>
       </c>
       <c r="J9" s="39" t="inlineStr">
         <is>
-          <t>Equal representation required by legislation</t>
+          <t>Non equal representation</t>
         </is>
       </c>
       <c r="K9" s="40" t="n">
-        <v>27970</v>
+        <v>573790</v>
       </c>
       <c r="L9" s="40" t="n">
-        <v>7656067</v>
+        <v>59958801</v>
       </c>
       <c r="M9" s="40" t="inlineStr">
         <is>
-          <t>$100,000 to $199,999</t>
+          <t>$40,000 to $59,999</t>
         </is>
       </c>
       <c r="N9" s="40" t="n">
-        <v>170089</v>
+        <v>48067</v>
       </c>
       <c r="O9" s="40" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P9" s="40" t="n">
-        <v>21540</v>
+        <v>346880</v>
       </c>
       <c r="Q9" s="40" t="n">
-        <v>6430</v>
+        <v>226910</v>
       </c>
       <c r="R9" s="40" t="n">
-        <v>6407580</v>
+        <v>42674891</v>
       </c>
       <c r="S9" s="40" t="n">
-        <v>1248488</v>
+        <v>17283909</v>
       </c>
       <c r="T9" s="40" t="n">
-        <v>297.5</v>
+        <v>123</v>
       </c>
       <c r="U9" s="40" t="n">
-        <v>194.2</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="10" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -11665,81 +11693,81 @@
       </c>
       <c r="B10" s="39" t="inlineStr">
         <is>
-          <t>ASGARD Independence Plan Division Two</t>
+          <t>ANZ Australian Staff Superannuation Scheme</t>
         </is>
       </c>
       <c r="C10" s="39" t="n">
-        <v>90194410365</v>
+        <v>83810127567</v>
       </c>
       <c r="D10" s="39" t="inlineStr">
         <is>
-          <t>public offer</t>
+          <t>non-public offer</t>
         </is>
       </c>
       <c r="E10" s="39" t="inlineStr">
         <is>
-          <t>RETAIL</t>
+          <t>CORPORATE</t>
         </is>
       </c>
       <c r="F10" s="39" t="inlineStr">
         <is>
-          <t>General base</t>
+          <t>Corporate base</t>
         </is>
       </c>
       <c r="G10" s="39" t="inlineStr">
         <is>
-          <t>BT Funds Management Limited</t>
+          <t>ANZ Staff Superannuation (Australia) Pty. Limited</t>
         </is>
       </c>
       <c r="H10" s="39" t="inlineStr">
         <is>
-          <t>Financial services corporation ownership</t>
+          <t>Employer sponsor (non-public sector) ownership</t>
         </is>
       </c>
       <c r="I10" s="39" t="inlineStr">
         <is>
-          <t>For profit status</t>
+          <t>Not for profit status</t>
         </is>
       </c>
       <c r="J10" s="39" t="inlineStr">
         <is>
-          <t>Non equal representation</t>
+          <t>Equal representation required by legislation</t>
         </is>
       </c>
       <c r="K10" s="40" t="n">
-        <v>229110</v>
+        <v>27970</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>81891949</v>
+        <v>7656067</v>
       </c>
       <c r="M10" s="40" t="inlineStr">
         <is>
-          <t>$200,000 to $499,999</t>
+          <t>$100,000 to $199,999</t>
         </is>
       </c>
       <c r="N10" s="40" t="n">
-        <v>240608</v>
+        <v>170089</v>
       </c>
       <c r="O10" s="40" t="n">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="P10" s="40" t="n">
-        <v>189360</v>
+        <v>21540</v>
       </c>
       <c r="Q10" s="40" t="n">
-        <v>39750</v>
+        <v>6430</v>
       </c>
       <c r="R10" s="40" t="n">
-        <v>67558907</v>
+        <v>6407580</v>
       </c>
       <c r="S10" s="40" t="n">
-        <v>14333042</v>
+        <v>1248488</v>
       </c>
       <c r="T10" s="40" t="n">
-        <v>356.8</v>
+        <v>297.5</v>
       </c>
       <c r="U10" s="40" t="n">
-        <v>360.6</v>
+        <v>194.2</v>
       </c>
     </row>
     <row r="11" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -11748,81 +11776,81 @@
       </c>
       <c r="B11" s="39" t="inlineStr">
         <is>
-          <t>Australian Defence Force Superannuation Scheme</t>
+          <t>ASGARD Independence Plan Division Two</t>
         </is>
       </c>
       <c r="C11" s="39" t="n">
-        <v>90302247344</v>
+        <v>90194410365</v>
       </c>
       <c r="D11" s="39" t="inlineStr">
         <is>
-          <t>non-public offer</t>
+          <t>public offer</t>
         </is>
       </c>
       <c r="E11" s="39" t="inlineStr">
         <is>
-          <t>PUBLIC_SECTOR</t>
+          <t>RETAIL</t>
         </is>
       </c>
       <c r="F11" s="39" t="inlineStr">
         <is>
-          <t>Government base</t>
+          <t>General base</t>
         </is>
       </c>
       <c r="G11" s="39" t="inlineStr">
         <is>
-          <t>Commonwealth Superannuation Corporation</t>
+          <t>BT Funds Management Limited</t>
         </is>
       </c>
       <c r="H11" s="39" t="inlineStr">
         <is>
-          <t>Public sector organisation ownership</t>
+          <t>Financial services corporation ownership</t>
         </is>
       </c>
       <c r="I11" s="39" t="inlineStr">
         <is>
-          <t>Not for profit status</t>
+          <t>For profit status</t>
         </is>
       </c>
       <c r="J11" s="39" t="inlineStr">
         <is>
-          <t>Equal representation required by legislation</t>
+          <t>Non equal representation</t>
         </is>
       </c>
       <c r="K11" s="40" t="n">
-        <v>44190</v>
+        <v>229110</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>3212802</v>
+        <v>81891949</v>
       </c>
       <c r="M11" s="40" t="inlineStr">
         <is>
-          <t>$60,000 to $99,999</t>
+          <t>$200,000 to $499,999</t>
         </is>
       </c>
       <c r="N11" s="40" t="n">
-        <v>61694</v>
+        <v>240608</v>
       </c>
       <c r="O11" s="40" t="n">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="P11" s="40" t="n">
-        <v>41140</v>
+        <v>189360</v>
       </c>
       <c r="Q11" s="40" t="n">
-        <v>3050</v>
+        <v>39750</v>
       </c>
       <c r="R11" s="40" t="n">
-        <v>3069955</v>
+        <v>67558907</v>
       </c>
       <c r="S11" s="40" t="n">
-        <v>142847</v>
+        <v>14333042</v>
       </c>
       <c r="T11" s="40" t="n">
-        <v>74.59999999999999</v>
+        <v>356.8</v>
       </c>
       <c r="U11" s="40" t="n">
-        <v>46.9</v>
+        <v>360.6</v>
       </c>
     </row>
     <row r="12" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -11831,81 +11859,81 @@
       </c>
       <c r="B12" s="39" t="inlineStr">
         <is>
-          <t>Australian Ethical Retail Superannuation Fund</t>
+          <t>Australian Defence Force Superannuation Scheme</t>
         </is>
       </c>
       <c r="C12" s="39" t="n">
-        <v>49633667743</v>
+        <v>90302247344</v>
       </c>
       <c r="D12" s="39" t="inlineStr">
         <is>
-          <t>public offer</t>
+          <t>non-public offer</t>
         </is>
       </c>
       <c r="E12" s="39" t="inlineStr">
         <is>
-          <t>RETAIL</t>
+          <t>PUBLIC_SECTOR</t>
         </is>
       </c>
       <c r="F12" s="39" t="inlineStr">
         <is>
-          <t>General base</t>
+          <t>Government base</t>
         </is>
       </c>
       <c r="G12" s="39" t="inlineStr">
         <is>
-          <t>Australian Ethical Superannuation Pty Ltd</t>
+          <t>Commonwealth Superannuation Corporation</t>
         </is>
       </c>
       <c r="H12" s="39" t="inlineStr">
         <is>
-          <t>Financial services corporation ownership</t>
+          <t>Public sector organisation ownership</t>
         </is>
       </c>
       <c r="I12" s="39" t="inlineStr">
         <is>
-          <t>For profit status</t>
+          <t>Not for profit status</t>
         </is>
       </c>
       <c r="J12" s="39" t="inlineStr">
         <is>
-          <t>Non equal representation</t>
+          <t>Equal representation required by legislation</t>
         </is>
       </c>
       <c r="K12" s="40" t="n">
-        <v>120610</v>
+        <v>44190</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>9976239</v>
+        <v>3212802</v>
       </c>
       <c r="M12" s="40" t="inlineStr">
         <is>
-          <t>$25,000 to $39,999</t>
+          <t>$60,000 to $99,999</t>
         </is>
       </c>
       <c r="N12" s="40" t="n">
-        <v>33145</v>
+        <v>61694</v>
       </c>
       <c r="O12" s="40" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="P12" s="40" t="n">
-        <v>97850</v>
+        <v>41140</v>
       </c>
       <c r="Q12" s="40" t="n">
-        <v>22760</v>
+        <v>3050</v>
       </c>
       <c r="R12" s="40" t="n">
-        <v>8379803</v>
+        <v>3069955</v>
       </c>
       <c r="S12" s="40" t="n">
-        <v>1596436</v>
+        <v>142847</v>
       </c>
       <c r="T12" s="40" t="n">
-        <v>85.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="U12" s="40" t="n">
-        <v>70.09999999999999</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="13" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -11914,11 +11942,11 @@
       </c>
       <c r="B13" s="39" t="inlineStr">
         <is>
-          <t>Australian Meat Industry Superannuation Trust</t>
+          <t>Australian Ethical Retail Superannuation Fund</t>
         </is>
       </c>
       <c r="C13" s="39" t="n">
-        <v>28342064803</v>
+        <v>49633667743</v>
       </c>
       <c r="D13" s="39" t="inlineStr">
         <is>
@@ -11927,68 +11955,68 @@
       </c>
       <c r="E13" s="39" t="inlineStr">
         <is>
-          <t>INDUSTRY</t>
+          <t>RETAIL</t>
         </is>
       </c>
       <c r="F13" s="39" t="inlineStr">
         <is>
-          <t>Industry base</t>
+          <t>General base</t>
         </is>
       </c>
       <c r="G13" s="39" t="inlineStr">
         <is>
-          <t>Australian Meat Industry Superannuation Pty Ltd</t>
+          <t>Australian Ethical Superannuation Pty Ltd</t>
         </is>
       </c>
       <c r="H13" s="39" t="inlineStr">
         <is>
-          <t>Nominating organisation ownership</t>
+          <t>Financial services corporation ownership</t>
         </is>
       </c>
       <c r="I13" s="39" t="inlineStr">
         <is>
-          <t>Not for profit status</t>
+          <t>For profit status</t>
         </is>
       </c>
       <c r="J13" s="39" t="inlineStr">
         <is>
-          <t>Equal representation required by governing rules</t>
+          <t>Non equal representation</t>
         </is>
       </c>
       <c r="K13" s="40" t="n">
-        <v>66310</v>
+        <v>120610</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>3571199</v>
+        <v>9976239</v>
       </c>
       <c r="M13" s="40" t="inlineStr">
         <is>
-          <t>$15,000 to $24,999</t>
+          <t>$25,000 to $39,999</t>
         </is>
       </c>
       <c r="N13" s="40" t="n">
-        <v>19099</v>
+        <v>33145</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P13" s="40" t="n">
-        <v>52110</v>
+        <v>97850</v>
       </c>
       <c r="Q13" s="40" t="n">
-        <v>14200</v>
+        <v>22760</v>
       </c>
       <c r="R13" s="40" t="n">
-        <v>3046755</v>
+        <v>8379803</v>
       </c>
       <c r="S13" s="40" t="n">
-        <v>524444</v>
+        <v>1596436</v>
       </c>
       <c r="T13" s="40" t="n">
-        <v>58.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="U13" s="40" t="n">
-        <v>36.9</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="14" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -11997,11 +12025,11 @@
       </c>
       <c r="B14" s="39" t="inlineStr">
         <is>
-          <t>Australian Retirement Trust</t>
+          <t>Australian Meat Industry Superannuation Trust</t>
         </is>
       </c>
       <c r="C14" s="39" t="n">
-        <v>60905115063</v>
+        <v>28342064803</v>
       </c>
       <c r="D14" s="39" t="inlineStr">
         <is>
@@ -12015,17 +12043,17 @@
       </c>
       <c r="F14" s="39" t="inlineStr">
         <is>
-          <t>General base</t>
+          <t>Industry base</t>
         </is>
       </c>
       <c r="G14" s="39" t="inlineStr">
         <is>
-          <t>Australian Retirement Trust Pty Ltd</t>
+          <t>Australian Meat Industry Superannuation Pty Ltd</t>
         </is>
       </c>
       <c r="H14" s="39" t="inlineStr">
         <is>
-          <t>Other ownership type</t>
+          <t>Nominating organisation ownership</t>
         </is>
       </c>
       <c r="I14" s="39" t="inlineStr">
@@ -12035,43 +12063,43 @@
       </c>
       <c r="J14" s="39" t="inlineStr">
         <is>
-          <t>Equal representation required by legislation</t>
+          <t>Equal representation required by governing rules</t>
         </is>
       </c>
       <c r="K14" s="40" t="n">
-        <v>2467980</v>
+        <v>66310</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>352036595</v>
+        <v>3571199</v>
       </c>
       <c r="M14" s="40" t="inlineStr">
         <is>
-          <t>$40,000 to $59,999</t>
+          <t>$15,000 to $24,999</t>
         </is>
       </c>
       <c r="N14" s="40" t="n">
-        <v>48655</v>
+        <v>19099</v>
       </c>
       <c r="O14" s="40" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="P14" s="40" t="n">
-        <v>2090040</v>
+        <v>52110</v>
       </c>
       <c r="Q14" s="40" t="n">
-        <v>377940</v>
+        <v>14200</v>
       </c>
       <c r="R14" s="40" t="n">
-        <v>319895309</v>
+        <v>3046755</v>
       </c>
       <c r="S14" s="40" t="n">
-        <v>32141286</v>
+        <v>524444</v>
       </c>
       <c r="T14" s="40" t="n">
-        <v>153.1</v>
+        <v>58.5</v>
       </c>
       <c r="U14" s="40" t="n">
-        <v>85</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="15" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -12080,11 +12108,11 @@
       </c>
       <c r="B15" s="39" t="inlineStr">
         <is>
-          <t>AustralianSuper</t>
+          <t>Australian Retirement Trust</t>
         </is>
       </c>
       <c r="C15" s="39" t="n">
-        <v>65714394898</v>
+        <v>60905115063</v>
       </c>
       <c r="D15" s="39" t="inlineStr">
         <is>
@@ -12103,12 +12131,12 @@
       </c>
       <c r="G15" s="39" t="inlineStr">
         <is>
-          <t>AustralianSuper Pty Ltd</t>
+          <t>Australian Retirement Trust Pty Ltd</t>
         </is>
       </c>
       <c r="H15" s="39" t="inlineStr">
         <is>
-          <t>Nominating organisation ownership</t>
+          <t>Other ownership type</t>
         </is>
       </c>
       <c r="I15" s="39" t="inlineStr">
@@ -12118,43 +12146,43 @@
       </c>
       <c r="J15" s="39" t="inlineStr">
         <is>
-          <t>Equal representation required by governing rules</t>
+          <t>Equal representation required by legislation</t>
         </is>
       </c>
       <c r="K15" s="40" t="n">
-        <v>3753760</v>
+        <v>2467980</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>410575693</v>
+        <v>352036595</v>
       </c>
       <c r="M15" s="40" t="inlineStr">
         <is>
-          <t>$25,000 to $39,999</t>
+          <t>$40,000 to $59,999</t>
         </is>
       </c>
       <c r="N15" s="40" t="n">
-        <v>31585</v>
+        <v>48655</v>
       </c>
       <c r="O15" s="40" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="P15" s="40" t="n">
-        <v>3196350</v>
+        <v>2090040</v>
       </c>
       <c r="Q15" s="40" t="n">
-        <v>557410</v>
+        <v>377940</v>
       </c>
       <c r="R15" s="40" t="n">
-        <v>363681055</v>
+        <v>319895309</v>
       </c>
       <c r="S15" s="40" t="n">
-        <v>46894638</v>
+        <v>32141286</v>
       </c>
       <c r="T15" s="40" t="n">
-        <v>113.8</v>
+        <v>153.1</v>
       </c>
       <c r="U15" s="40" t="n">
-        <v>84.09999999999999</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -12163,11 +12191,11 @@
       </c>
       <c r="B16" s="39" t="inlineStr">
         <is>
-          <t>AvWrap Retirement Service</t>
+          <t>AustralianSuper</t>
         </is>
       </c>
       <c r="C16" s="39" t="n">
-        <v>82004832237</v>
+        <v>65714394898</v>
       </c>
       <c r="D16" s="39" t="inlineStr">
         <is>
@@ -12176,7 +12204,7 @@
       </c>
       <c r="E16" s="39" t="inlineStr">
         <is>
-          <t>RETAIL</t>
+          <t>INDUSTRY</t>
         </is>
       </c>
       <c r="F16" s="39" t="inlineStr">
@@ -12186,58 +12214,58 @@
       </c>
       <c r="G16" s="39" t="inlineStr">
         <is>
-          <t>I.O.O.F. Investment Management Limited</t>
+          <t>AustralianSuper Pty Ltd</t>
         </is>
       </c>
       <c r="H16" s="39" t="inlineStr">
         <is>
-          <t>Financial services corporation ownership</t>
+          <t>Nominating organisation ownership</t>
         </is>
       </c>
       <c r="I16" s="39" t="inlineStr">
         <is>
-          <t>For profit status</t>
+          <t>Not for profit status</t>
         </is>
       </c>
       <c r="J16" s="39" t="inlineStr">
         <is>
-          <t>Non equal representation</t>
+          <t>Equal representation required by governing rules</t>
         </is>
       </c>
       <c r="K16" s="40" t="n">
-        <v>4890</v>
+        <v>3753760</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>1730116</v>
+        <v>410575693</v>
       </c>
       <c r="M16" s="40" t="inlineStr">
         <is>
-          <t>$200,000 to $499,999</t>
+          <t>$25,000 to $39,999</t>
         </is>
       </c>
       <c r="N16" s="40" t="n">
-        <v>224520</v>
+        <v>31585</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="P16" s="40" t="n">
-        <v>4890</v>
+        <v>3196350</v>
       </c>
       <c r="Q16" s="40" t="n">
-        <v>0</v>
+        <v>557410</v>
       </c>
       <c r="R16" s="40" t="n">
-        <v>1730116</v>
+        <v>363681055</v>
       </c>
       <c r="S16" s="40" t="n">
-        <v>0</v>
+        <v>46894638</v>
       </c>
       <c r="T16" s="40" t="n">
-        <v>353.5</v>
+        <v>113.8</v>
       </c>
       <c r="U16" s="40" t="n">
-        <v>0</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="17" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -12246,11 +12274,11 @@
       </c>
       <c r="B17" s="39" t="inlineStr">
         <is>
-          <t>Avanteos Superannuation Trust</t>
+          <t>AvWrap Retirement Service</t>
         </is>
       </c>
       <c r="C17" s="39" t="n">
-        <v>38876896681</v>
+        <v>82004832237</v>
       </c>
       <c r="D17" s="39" t="inlineStr">
         <is>
@@ -12269,7 +12297,7 @@
       </c>
       <c r="G17" s="39" t="inlineStr">
         <is>
-          <t>Avanteos Investments Limited</t>
+          <t>I.O.O.F. Investment Management Limited</t>
         </is>
       </c>
       <c r="H17" s="39" t="inlineStr">
@@ -12288,10 +12316,10 @@
         </is>
       </c>
       <c r="K17" s="40" t="n">
-        <v>43280</v>
+        <v>4890</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>17503521</v>
+        <v>1730116</v>
       </c>
       <c r="M17" s="40" t="inlineStr">
         <is>
@@ -12299,28 +12327,28 @@
         </is>
       </c>
       <c r="N17" s="40" t="n">
-        <v>294568</v>
+        <v>224520</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="P17" s="40" t="n">
-        <v>42740</v>
+        <v>4890</v>
       </c>
       <c r="Q17" s="40" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="R17" s="40" t="n">
-        <v>17376516</v>
+        <v>1730116</v>
       </c>
       <c r="S17" s="40" t="n">
-        <v>127005</v>
+        <v>0</v>
       </c>
       <c r="T17" s="40" t="n">
-        <v>406.6</v>
+        <v>353.5</v>
       </c>
       <c r="U17" s="40" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -12329,11 +12357,11 @@
       </c>
       <c r="B18" s="39" t="inlineStr">
         <is>
-          <t>Aware Super</t>
+          <t>Avanteos Superannuation Trust</t>
         </is>
       </c>
       <c r="C18" s="39" t="n">
-        <v>53226460365</v>
+        <v>38876896681</v>
       </c>
       <c r="D18" s="39" t="inlineStr">
         <is>
@@ -12342,68 +12370,68 @@
       </c>
       <c r="E18" s="39" t="inlineStr">
         <is>
-          <t>PUBLIC_SECTOR</t>
+          <t>RETAIL</t>
         </is>
       </c>
       <c r="F18" s="39" t="inlineStr">
         <is>
-          <t>Government base</t>
+          <t>General base</t>
         </is>
       </c>
       <c r="G18" s="39" t="inlineStr">
         <is>
-          <t>Aware Super Pty Ltd</t>
+          <t>Avanteos Investments Limited</t>
         </is>
       </c>
       <c r="H18" s="39" t="inlineStr">
         <is>
-          <t>Other ownership type</t>
+          <t>Financial services corporation ownership</t>
         </is>
       </c>
       <c r="I18" s="39" t="inlineStr">
         <is>
-          <t>Not for profit status</t>
+          <t>For profit status</t>
         </is>
       </c>
       <c r="J18" s="39" t="inlineStr">
         <is>
-          <t>Equal representation required by governing rules</t>
+          <t>Non equal representation</t>
         </is>
       </c>
       <c r="K18" s="40" t="n">
-        <v>1244940</v>
+        <v>43280</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>208241132</v>
+        <v>17503521</v>
       </c>
       <c r="M18" s="40" t="inlineStr">
         <is>
-          <t>$60,000 to $99,999</t>
+          <t>$200,000 to $499,999</t>
         </is>
       </c>
       <c r="N18" s="40" t="n">
-        <v>86286</v>
+        <v>294568</v>
       </c>
       <c r="O18" s="40" t="n">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="P18" s="40" t="n">
-        <v>1056840</v>
+        <v>42740</v>
       </c>
       <c r="Q18" s="40" t="n">
-        <v>188100</v>
+        <v>550</v>
       </c>
       <c r="R18" s="40" t="n">
-        <v>190710294</v>
+        <v>17376516</v>
       </c>
       <c r="S18" s="40" t="n">
-        <v>17530838</v>
+        <v>127005</v>
       </c>
       <c r="T18" s="40" t="n">
-        <v>180.5</v>
+        <v>406.6</v>
       </c>
       <c r="U18" s="40" t="n">
-        <v>93.2</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -12412,11 +12440,11 @@
       </c>
       <c r="B19" s="39" t="inlineStr">
         <is>
-          <t>Brighter Super Fund</t>
+          <t>Aware Super</t>
         </is>
       </c>
       <c r="C19" s="39" t="n">
-        <v>23053121564</v>
+        <v>53226460365</v>
       </c>
       <c r="D19" s="39" t="inlineStr">
         <is>
@@ -12430,17 +12458,17 @@
       </c>
       <c r="F19" s="39" t="inlineStr">
         <is>
-          <t>General base</t>
+          <t>Government base</t>
         </is>
       </c>
       <c r="G19" s="39" t="inlineStr">
         <is>
-          <t>Brighter Super Trustee</t>
+          <t>Aware Super Pty Ltd</t>
         </is>
       </c>
       <c r="H19" s="39" t="inlineStr">
         <is>
-          <t>Public sector organisation ownership</t>
+          <t>Other ownership type</t>
         </is>
       </c>
       <c r="I19" s="39" t="inlineStr">
@@ -12454,39 +12482,39 @@
         </is>
       </c>
       <c r="K19" s="40" t="n">
-        <v>382970</v>
+        <v>1244940</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>36442844</v>
+        <v>208241132</v>
       </c>
       <c r="M19" s="40" t="inlineStr">
         <is>
-          <t>$1,000 to $5,999</t>
+          <t>$60,000 to $99,999</t>
         </is>
       </c>
       <c r="N19" s="40" t="n">
-        <v>1417</v>
+        <v>86286</v>
       </c>
       <c r="O19" s="40" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P19" s="40" t="n">
-        <v>294450</v>
+        <v>1056840</v>
       </c>
       <c r="Q19" s="40" t="n">
-        <v>88520</v>
+        <v>188100</v>
       </c>
       <c r="R19" s="40" t="n">
-        <v>32013134</v>
+        <v>190710294</v>
       </c>
       <c r="S19" s="40" t="n">
-        <v>4429709</v>
+        <v>17530838</v>
       </c>
       <c r="T19" s="40" t="n">
-        <v>108.7</v>
+        <v>180.5</v>
       </c>
       <c r="U19" s="40" t="n">
-        <v>50</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="20" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -12495,11 +12523,11 @@
       </c>
       <c r="B20" s="39" t="inlineStr">
         <is>
-          <t>Building Unions Superannuation Scheme (Queensland)</t>
+          <t>Brighter Super Fund</t>
         </is>
       </c>
       <c r="C20" s="39" t="n">
-        <v>85571332201</v>
+        <v>23053121564</v>
       </c>
       <c r="D20" s="39" t="inlineStr">
         <is>
@@ -12508,22 +12536,22 @@
       </c>
       <c r="E20" s="39" t="inlineStr">
         <is>
-          <t>INDUSTRY</t>
+          <t>PUBLIC_SECTOR</t>
         </is>
       </c>
       <c r="F20" s="39" t="inlineStr">
         <is>
-          <t>Industry base</t>
+          <t>General base</t>
         </is>
       </c>
       <c r="G20" s="39" t="inlineStr">
         <is>
-          <t>BUSS (Queensland) Pty Ltd</t>
+          <t>Brighter Super Trustee</t>
         </is>
       </c>
       <c r="H20" s="39" t="inlineStr">
         <is>
-          <t>Nominating organisation ownership</t>
+          <t>Public sector organisation ownership</t>
         </is>
       </c>
       <c r="I20" s="39" t="inlineStr">
@@ -12537,39 +12565,39 @@
         </is>
       </c>
       <c r="K20" s="40" t="n">
-        <v>70900</v>
+        <v>382970</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>7489956</v>
+        <v>36442844</v>
       </c>
       <c r="M20" s="40" t="inlineStr">
         <is>
-          <t>$40,000 to $59,999</t>
+          <t>$1,000 to $5,999</t>
         </is>
       </c>
       <c r="N20" s="40" t="n">
-        <v>48625</v>
+        <v>1417</v>
       </c>
       <c r="O20" s="40" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="P20" s="40" t="n">
-        <v>53740</v>
+        <v>294450</v>
       </c>
       <c r="Q20" s="40" t="n">
-        <v>17160</v>
+        <v>88520</v>
       </c>
       <c r="R20" s="40" t="n">
-        <v>6558067</v>
+        <v>32013134</v>
       </c>
       <c r="S20" s="40" t="n">
-        <v>931889</v>
+        <v>4429709</v>
       </c>
       <c r="T20" s="40" t="n">
-        <v>122</v>
+        <v>108.7</v>
       </c>
       <c r="U20" s="40" t="n">
-        <v>54.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -12578,11 +12606,11 @@
       </c>
       <c r="B21" s="39" t="inlineStr">
         <is>
-          <t>CONSTRUCTION AND BUILDING UNIONS SUPERANNUATION FUND</t>
+          <t>Building Unions Superannuation Scheme (Queensland)</t>
         </is>
       </c>
       <c r="C21" s="39" t="n">
-        <v>75493363262</v>
+        <v>85571332201</v>
       </c>
       <c r="D21" s="39" t="inlineStr">
         <is>
@@ -12601,7 +12629,7 @@
       </c>
       <c r="G21" s="39" t="inlineStr">
         <is>
-          <t>United Super Pty Ltd</t>
+          <t>BUSS (Queensland) Pty Ltd</t>
         </is>
       </c>
       <c r="H21" s="39" t="inlineStr">
@@ -12620,10 +12648,10 @@
         </is>
       </c>
       <c r="K21" s="40" t="n">
-        <v>927390</v>
+        <v>70900</v>
       </c>
       <c r="L21" s="40" t="n">
-        <v>106541394</v>
+        <v>7489956</v>
       </c>
       <c r="M21" s="40" t="inlineStr">
         <is>
@@ -12631,28 +12659,28 @@
         </is>
       </c>
       <c r="N21" s="40" t="n">
-        <v>49744</v>
+        <v>48625</v>
       </c>
       <c r="O21" s="40" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="P21" s="40" t="n">
-        <v>749360</v>
+        <v>53740</v>
       </c>
       <c r="Q21" s="40" t="n">
-        <v>178030</v>
+        <v>17160</v>
       </c>
       <c r="R21" s="40" t="n">
-        <v>93664122</v>
+        <v>6558067</v>
       </c>
       <c r="S21" s="40" t="n">
-        <v>12877271</v>
+        <v>931889</v>
       </c>
       <c r="T21" s="40" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="U21" s="40" t="n">
-        <v>72.3</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="22" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -12661,35 +12689,35 @@
       </c>
       <c r="B22" s="39" t="inlineStr">
         <is>
-          <t>CSS Fund</t>
+          <t>CONSTRUCTION AND BUILDING UNIONS SUPERANNUATION FUND</t>
         </is>
       </c>
       <c r="C22" s="39" t="n">
-        <v>19415776361</v>
+        <v>75493363262</v>
       </c>
       <c r="D22" s="39" t="inlineStr">
         <is>
-          <t>non-public offer</t>
+          <t>public offer</t>
         </is>
       </c>
       <c r="E22" s="39" t="inlineStr">
         <is>
-          <t>PUBLIC_SECTOR</t>
+          <t>INDUSTRY</t>
         </is>
       </c>
       <c r="F22" s="39" t="inlineStr">
         <is>
-          <t>Government base</t>
+          <t>Industry base</t>
         </is>
       </c>
       <c r="G22" s="39" t="inlineStr">
         <is>
-          <t>Commonwealth Superannuation Corporation</t>
+          <t>United Super Pty Ltd</t>
         </is>
       </c>
       <c r="H22" s="39" t="inlineStr">
         <is>
-          <t>Public sector organisation ownership</t>
+          <t>Nominating organisation ownership</t>
         </is>
       </c>
       <c r="I22" s="39" t="inlineStr">
@@ -12699,43 +12727,43 @@
       </c>
       <c r="J22" s="39" t="inlineStr">
         <is>
-          <t>Equal representation required by legislation</t>
+          <t>Equal representation required by governing rules</t>
         </is>
       </c>
       <c r="K22" s="40" t="n">
-        <v>92000</v>
+        <v>927390</v>
       </c>
       <c r="L22" s="40" t="n">
-        <v>61396742</v>
+        <v>106541394</v>
       </c>
       <c r="M22" s="40" t="inlineStr">
         <is>
-          <t>$500,000 to $999,999</t>
+          <t>$40,000 to $59,999</t>
         </is>
       </c>
       <c r="N22" s="40" t="n">
-        <v>586952</v>
+        <v>49744</v>
       </c>
       <c r="O22" s="40" t="n">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="P22" s="40" t="n">
-        <v>92000</v>
+        <v>749360</v>
       </c>
       <c r="Q22" s="40" t="n">
-        <v>0</v>
+        <v>178030</v>
       </c>
       <c r="R22" s="40" t="n">
-        <v>61396742</v>
+        <v>93664122</v>
       </c>
       <c r="S22" s="40" t="n">
-        <v>0</v>
+        <v>12877271</v>
       </c>
       <c r="T22" s="40" t="n">
-        <v>667.4</v>
+        <v>125</v>
       </c>
       <c r="U22" s="40" t="n">
-        <v>0</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="23" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -12744,35 +12772,35 @@
       </c>
       <c r="B23" s="39" t="inlineStr">
         <is>
-          <t>CareSuper</t>
+          <t>CSS Fund</t>
         </is>
       </c>
       <c r="C23" s="39" t="n">
-        <v>74559365913</v>
+        <v>19415776361</v>
       </c>
       <c r="D23" s="39" t="inlineStr">
         <is>
-          <t>public offer</t>
+          <t>non-public offer</t>
         </is>
       </c>
       <c r="E23" s="39" t="inlineStr">
         <is>
-          <t>INDUSTRY</t>
+          <t>PUBLIC_SECTOR</t>
         </is>
       </c>
       <c r="F23" s="39" t="inlineStr">
         <is>
-          <t>General base</t>
-        </is>
-      </c>
-      <c r="G23" s="82" t="inlineStr">
-        <is>
-          <t>CareSuper Pty Ltd</t>
+          <t>Government base</t>
+        </is>
+      </c>
+      <c r="G23" s="39" t="inlineStr">
+        <is>
+          <t>Commonwealth Superannuation Corporation</t>
         </is>
       </c>
       <c r="H23" s="39" t="inlineStr">
         <is>
-          <t>Employer sponsor (non-public sector) ownership</t>
+          <t>Public sector organisation ownership</t>
         </is>
       </c>
       <c r="I23" s="39" t="inlineStr">
@@ -12786,39 +12814,39 @@
         </is>
       </c>
       <c r="K23" s="40" t="n">
-        <v>625630</v>
+        <v>92000</v>
       </c>
       <c r="L23" s="40" t="n">
-        <v>61738883</v>
+        <v>61396742</v>
       </c>
       <c r="M23" s="40" t="inlineStr">
         <is>
-          <t>$25,000 to $39,999</t>
+          <t>$500,000 to $999,999</t>
         </is>
       </c>
       <c r="N23" s="40" t="n">
-        <v>36788</v>
+        <v>586952</v>
       </c>
       <c r="O23" s="40" t="n">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="P23" s="40" t="n">
-        <v>563750</v>
+        <v>92000</v>
       </c>
       <c r="Q23" s="40" t="n">
-        <v>61880</v>
+        <v>0</v>
       </c>
       <c r="R23" s="40" t="n">
-        <v>58122522</v>
+        <v>61396742</v>
       </c>
       <c r="S23" s="40" t="n">
-        <v>3616361</v>
+        <v>0</v>
       </c>
       <c r="T23" s="40" t="n">
-        <v>103.1</v>
+        <v>667.4</v>
       </c>
       <c r="U23" s="40" t="n">
-        <v>58.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -12827,11 +12855,11 @@
       </c>
       <c r="B24" s="39" t="inlineStr">
         <is>
-          <t>Centric Super Fund</t>
+          <t>CareSuper</t>
         </is>
       </c>
       <c r="C24" s="39" t="n">
-        <v>91593544166</v>
+        <v>74559365913</v>
       </c>
       <c r="D24" s="39" t="inlineStr">
         <is>
@@ -12840,7 +12868,7 @@
       </c>
       <c r="E24" s="39" t="inlineStr">
         <is>
-          <t>RETAIL</t>
+          <t>INDUSTRY</t>
         </is>
       </c>
       <c r="F24" s="39" t="inlineStr">
@@ -12848,60 +12876,60 @@
           <t>General base</t>
         </is>
       </c>
-      <c r="G24" s="39" t="inlineStr">
-        <is>
-          <t>Equity Trustees Superannuation Limited</t>
+      <c r="G24" s="82" t="inlineStr">
+        <is>
+          <t>CareSuper Pty Ltd</t>
         </is>
       </c>
       <c r="H24" s="39" t="inlineStr">
         <is>
-          <t>Financial services corporation ownership</t>
+          <t>Employer sponsor (non-public sector) ownership</t>
         </is>
       </c>
       <c r="I24" s="39" t="inlineStr">
         <is>
-          <t>For profit status</t>
+          <t>Not for profit status</t>
         </is>
       </c>
       <c r="J24" s="39" t="inlineStr">
         <is>
-          <t>Non equal representation</t>
+          <t>Equal representation required by legislation</t>
         </is>
       </c>
       <c r="K24" s="40" t="n">
-        <v>9800</v>
+        <v>625630</v>
       </c>
       <c r="L24" s="40" t="n">
-        <v>4266370</v>
+        <v>61738883</v>
       </c>
       <c r="M24" s="40" t="inlineStr">
         <is>
-          <t>$200,000 to $499,999</t>
+          <t>$25,000 to $39,999</t>
         </is>
       </c>
       <c r="N24" s="40" t="n">
-        <v>324688</v>
+        <v>36788</v>
       </c>
       <c r="O24" s="40" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="P24" s="40" t="n">
-        <v>8800</v>
+        <v>563750</v>
       </c>
       <c r="Q24" s="40" t="n">
-        <v>1000</v>
+        <v>61880</v>
       </c>
       <c r="R24" s="40" t="n">
-        <v>3803888</v>
+        <v>58122522</v>
       </c>
       <c r="S24" s="40" t="n">
-        <v>462482</v>
+        <v>3616361</v>
       </c>
       <c r="T24" s="40" t="n">
-        <v>432.2</v>
+        <v>103.1</v>
       </c>
       <c r="U24" s="40" t="n">
-        <v>464.3</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="25" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -12910,11 +12938,11 @@
       </c>
       <c r="B25" s="39" t="inlineStr">
         <is>
-          <t>Challenger Retirement Fund</t>
+          <t>Centric Super Fund</t>
         </is>
       </c>
       <c r="C25" s="39" t="n">
-        <v>87883998803</v>
+        <v>91593544166</v>
       </c>
       <c r="D25" s="39" t="inlineStr">
         <is>
@@ -12933,7 +12961,7 @@
       </c>
       <c r="G25" s="39" t="inlineStr">
         <is>
-          <t>Challenger Retirement and Investment Services Limited</t>
+          <t>Equity Trustees Superannuation Limited</t>
         </is>
       </c>
       <c r="H25" s="39" t="inlineStr">
@@ -12952,39 +12980,39 @@
         </is>
       </c>
       <c r="K25" s="40" t="n">
-        <v>2620</v>
+        <v>9800</v>
       </c>
       <c r="L25" s="40" t="n">
-        <v>343371</v>
+        <v>4266370</v>
       </c>
       <c r="M25" s="40" t="inlineStr">
         <is>
-          <t>$60,000 to $99,999</t>
+          <t>$200,000 to $499,999</t>
         </is>
       </c>
       <c r="N25" s="40" t="n">
-        <v>70795</v>
+        <v>324688</v>
       </c>
       <c r="O25" s="40" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="P25" s="40" t="n">
-        <v>2620</v>
+        <v>8800</v>
       </c>
       <c r="Q25" s="40" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="R25" s="40" t="n">
-        <v>343371</v>
+        <v>3803888</v>
       </c>
       <c r="S25" s="40" t="n">
-        <v>0</v>
+        <v>462482</v>
       </c>
       <c r="T25" s="40" t="n">
-        <v>131</v>
+        <v>432.2</v>
       </c>
       <c r="U25" s="40" t="n">
-        <v>0</v>
+        <v>464.3</v>
       </c>
     </row>
     <row r="26" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -12993,11 +13021,11 @@
       </c>
       <c r="B26" s="39" t="inlineStr">
         <is>
-          <t>Colonial First State FirstChoice Superannuation Trust</t>
+          <t>Challenger Retirement Fund</t>
         </is>
       </c>
       <c r="C26" s="39" t="n">
-        <v>26458298557</v>
+        <v>87883998803</v>
       </c>
       <c r="D26" s="39" t="inlineStr">
         <is>
@@ -13016,7 +13044,7 @@
       </c>
       <c r="G26" s="39" t="inlineStr">
         <is>
-          <t>Avanteos Investments Limited</t>
+          <t>Challenger Retirement and Investment Services Limited</t>
         </is>
       </c>
       <c r="H26" s="39" t="inlineStr">
@@ -13035,39 +13063,39 @@
         </is>
       </c>
       <c r="K26" s="40" t="n">
-        <v>610120</v>
+        <v>2620</v>
       </c>
       <c r="L26" s="40" t="n">
-        <v>111158082</v>
+        <v>343371</v>
       </c>
       <c r="M26" s="40" t="inlineStr">
         <is>
-          <t>$100,000 to $199,999</t>
+          <t>$60,000 to $99,999</t>
         </is>
       </c>
       <c r="N26" s="40" t="n">
-        <v>106567</v>
+        <v>70795</v>
       </c>
       <c r="O26" s="40" t="n">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="P26" s="40" t="n">
-        <v>464140</v>
+        <v>2620</v>
       </c>
       <c r="Q26" s="40" t="n">
-        <v>145990</v>
+        <v>0</v>
       </c>
       <c r="R26" s="40" t="n">
-        <v>97341357</v>
+        <v>343371</v>
       </c>
       <c r="S26" s="40" t="n">
-        <v>13816726</v>
+        <v>0</v>
       </c>
       <c r="T26" s="40" t="n">
-        <v>209.7</v>
+        <v>131</v>
       </c>
       <c r="U26" s="40" t="n">
-        <v>94.59999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -13076,81 +13104,81 @@
       </c>
       <c r="B27" s="39" t="inlineStr">
         <is>
-          <t>Crown Employees (NSW Fire Brigades Firefighting Staff Death &amp; Disability) Superannuation Fund</t>
+          <t>Colonial First State FirstChoice Superannuation Trust</t>
         </is>
       </c>
       <c r="C27" s="39" t="n">
-        <v>60532453567</v>
+        <v>26458298557</v>
       </c>
       <c r="D27" s="39" t="inlineStr">
         <is>
-          <t>non-public offer</t>
+          <t>public offer</t>
         </is>
       </c>
       <c r="E27" s="39" t="inlineStr">
         <is>
-          <t>PUBLIC_SECTOR</t>
+          <t>RETAIL</t>
         </is>
       </c>
       <c r="F27" s="39" t="inlineStr">
         <is>
-          <t>Government base</t>
+          <t>General base</t>
         </is>
       </c>
       <c r="G27" s="39" t="inlineStr">
         <is>
-          <t>NSW Fire Brigades Superannuation Pty Limited</t>
+          <t>Avanteos Investments Limited</t>
         </is>
       </c>
       <c r="H27" s="39" t="inlineStr">
         <is>
-          <t>Public sector organisation ownership</t>
+          <t>Financial services corporation ownership</t>
         </is>
       </c>
       <c r="I27" s="39" t="inlineStr">
         <is>
-          <t>Not for profit status</t>
+          <t>For profit status</t>
         </is>
       </c>
       <c r="J27" s="39" t="inlineStr">
         <is>
-          <t>Equal representation required by legislation</t>
+          <t>Non equal representation</t>
         </is>
       </c>
       <c r="K27" s="40" t="n">
-        <v>7020</v>
+        <v>610120</v>
       </c>
       <c r="L27" s="40" t="n">
-        <v>0</v>
+        <v>111158082</v>
       </c>
       <c r="M27" s="40" t="inlineStr">
         <is>
-          <t>&lt;$1,000</t>
+          <t>$100,000 to $199,999</t>
         </is>
       </c>
       <c r="N27" s="40" t="n">
-        <v>0</v>
+        <v>106567</v>
       </c>
       <c r="O27" s="40" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="P27" s="40" t="n">
-        <v>6810</v>
+        <v>464140</v>
       </c>
       <c r="Q27" s="40" t="n">
-        <v>220</v>
+        <v>145990</v>
       </c>
       <c r="R27" s="40" t="n">
-        <v>0</v>
+        <v>97341357</v>
       </c>
       <c r="S27" s="40" t="n">
-        <v>0</v>
+        <v>13816726</v>
       </c>
       <c r="T27" s="40" t="n">
-        <v>0</v>
+        <v>209.7</v>
       </c>
       <c r="U27" s="40" t="n">
-        <v>0</v>
+        <v>94.59999999999999</v>
       </c>
     </row>
     <row r="28" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -13159,81 +13187,81 @@
       </c>
       <c r="B28" s="39" t="inlineStr">
         <is>
-          <t>Essential Super</t>
+          <t>Crown Employees (NSW Fire Brigades Firefighting Staff Death &amp; Disability) Superannuation Fund</t>
         </is>
       </c>
       <c r="C28" s="39" t="n">
-        <v>56601925435</v>
+        <v>60532453567</v>
       </c>
       <c r="D28" s="39" t="inlineStr">
         <is>
-          <t>public offer</t>
+          <t>non-public offer</t>
         </is>
       </c>
       <c r="E28" s="39" t="inlineStr">
         <is>
-          <t>RETAIL</t>
+          <t>PUBLIC_SECTOR</t>
         </is>
       </c>
       <c r="F28" s="39" t="inlineStr">
         <is>
-          <t>General base</t>
+          <t>Government base</t>
         </is>
       </c>
       <c r="G28" s="39" t="inlineStr">
         <is>
-          <t>Avanteos Investments Limited</t>
+          <t>NSW Fire Brigades Superannuation Pty Limited</t>
         </is>
       </c>
       <c r="H28" s="39" t="inlineStr">
         <is>
-          <t>Financial services corporation ownership</t>
+          <t>Public sector organisation ownership</t>
         </is>
       </c>
       <c r="I28" s="39" t="inlineStr">
         <is>
-          <t>For profit status</t>
+          <t>Not for profit status</t>
         </is>
       </c>
       <c r="J28" s="39" t="inlineStr">
         <is>
-          <t>Non equal representation</t>
+          <t>Equal representation required by legislation</t>
         </is>
       </c>
       <c r="K28" s="40" t="n">
-        <v>140520</v>
+        <v>7020</v>
       </c>
       <c r="L28" s="40" t="n">
-        <v>7059577</v>
+        <v>0</v>
       </c>
       <c r="M28" s="40" t="inlineStr">
         <is>
-          <t>$25,000 to $39,999</t>
+          <t>&lt;$1,000</t>
         </is>
       </c>
       <c r="N28" s="40" t="n">
-        <v>31128</v>
+        <v>0</v>
       </c>
       <c r="O28" s="40" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="P28" s="40" t="n">
-        <v>110040</v>
+        <v>6810</v>
       </c>
       <c r="Q28" s="40" t="n">
-        <v>30480</v>
+        <v>220</v>
       </c>
       <c r="R28" s="40" t="n">
-        <v>5941328</v>
+        <v>0</v>
       </c>
       <c r="S28" s="40" t="n">
-        <v>1118249</v>
+        <v>0</v>
       </c>
       <c r="T28" s="40" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="U28" s="40" t="n">
-        <v>36.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -13242,11 +13270,11 @@
       </c>
       <c r="B29" s="39" t="inlineStr">
         <is>
-          <t>Fiducian Superannuation Fund</t>
+          <t>Essential Super</t>
         </is>
       </c>
       <c r="C29" s="39" t="n">
-        <v>57929339093</v>
+        <v>56601925435</v>
       </c>
       <c r="D29" s="39" t="inlineStr">
         <is>
@@ -13265,7 +13293,7 @@
       </c>
       <c r="G29" s="39" t="inlineStr">
         <is>
-          <t>Fiducian Portfolio Services Limited</t>
+          <t>Avanteos Investments Limited</t>
         </is>
       </c>
       <c r="H29" s="39" t="inlineStr">
@@ -13284,45 +13312,39 @@
         </is>
       </c>
       <c r="K29" s="40" t="n">
-        <v>9780</v>
+        <v>140520</v>
       </c>
       <c r="L29" s="40" t="n">
-        <v>3124129</v>
+        <v>7059577</v>
       </c>
       <c r="M29" s="40" t="inlineStr">
         <is>
-          <t>$200,000 to $499,999</t>
+          <t>$25,000 to $39,999</t>
         </is>
       </c>
       <c r="N29" s="40" t="n">
-        <v>237405</v>
+        <v>31128</v>
       </c>
       <c r="O29" s="40" t="n">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="P29" s="40" t="n">
-        <v>9780</v>
-      </c>
-      <c r="Q29" s="40" t="inlineStr">
-        <is>
-          <t>&lt;20</t>
-        </is>
+        <v>110040</v>
+      </c>
+      <c r="Q29" s="40" t="n">
+        <v>30480</v>
       </c>
       <c r="R29" s="40" t="n">
-        <v>3124123</v>
-      </c>
-      <c r="S29" s="40" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
+        <v>5941328</v>
+      </c>
+      <c r="S29" s="40" t="n">
+        <v>1118249</v>
       </c>
       <c r="T29" s="40" t="n">
-        <v>319.5</v>
-      </c>
-      <c r="U29" s="40" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
+        <v>54</v>
+      </c>
+      <c r="U29" s="40" t="n">
+        <v>36.7</v>
       </c>
     </row>
     <row r="30" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -13331,52 +13353,52 @@
       </c>
       <c r="B30" s="39" t="inlineStr">
         <is>
-          <t>Fire and Emergency Services Superannuation Fund</t>
+          <t>Fiducian Superannuation Fund</t>
         </is>
       </c>
       <c r="C30" s="39" t="n">
-        <v>43198502058</v>
+        <v>57929339093</v>
       </c>
       <c r="D30" s="39" t="inlineStr">
         <is>
-          <t>non-public offer</t>
+          <t>public offer</t>
         </is>
       </c>
       <c r="E30" s="39" t="inlineStr">
         <is>
-          <t>PUBLIC_SECTOR</t>
+          <t>RETAIL</t>
         </is>
       </c>
       <c r="F30" s="39" t="inlineStr">
         <is>
-          <t>Government base</t>
+          <t>General base</t>
         </is>
       </c>
       <c r="G30" s="39" t="inlineStr">
         <is>
-          <t>Fire and Emergency Services Superannuation Board</t>
+          <t>Fiducian Portfolio Services Limited</t>
         </is>
       </c>
       <c r="H30" s="39" t="inlineStr">
         <is>
-          <t>Public sector organisation ownership</t>
+          <t>Financial services corporation ownership</t>
         </is>
       </c>
       <c r="I30" s="39" t="inlineStr">
         <is>
-          <t>Not for profit status</t>
+          <t>For profit status</t>
         </is>
       </c>
       <c r="J30" s="39" t="inlineStr">
         <is>
-          <t>Equal representation required by legislation</t>
+          <t>Non equal representation</t>
         </is>
       </c>
       <c r="K30" s="40" t="n">
-        <v>2660</v>
+        <v>9780</v>
       </c>
       <c r="L30" s="40" t="n">
-        <v>939347</v>
+        <v>3124129</v>
       </c>
       <c r="M30" s="40" t="inlineStr">
         <is>
@@ -13384,28 +13406,34 @@
         </is>
       </c>
       <c r="N30" s="40" t="n">
-        <v>252882</v>
+        <v>237405</v>
       </c>
       <c r="O30" s="40" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="P30" s="40" t="n">
-        <v>1910</v>
-      </c>
-      <c r="Q30" s="40" t="n">
-        <v>760</v>
+        <v>9780</v>
+      </c>
+      <c r="Q30" s="40" t="inlineStr">
+        <is>
+          <t>&lt;20</t>
+        </is>
       </c>
       <c r="R30" s="40" t="n">
-        <v>654360</v>
-      </c>
-      <c r="S30" s="40" t="n">
-        <v>284988</v>
+        <v>3124123</v>
+      </c>
+      <c r="S30" s="40" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
       </c>
       <c r="T30" s="40" t="n">
-        <v>343.3</v>
-      </c>
-      <c r="U30" s="40" t="n">
-        <v>376.5</v>
+        <v>319.5</v>
+      </c>
+      <c r="U30" s="40" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -13414,35 +13442,35 @@
       </c>
       <c r="B31" s="39" t="inlineStr">
         <is>
-          <t>First Super</t>
+          <t>Fire and Emergency Services Superannuation Fund</t>
         </is>
       </c>
       <c r="C31" s="39" t="n">
-        <v>56286625181</v>
+        <v>43198502058</v>
       </c>
       <c r="D31" s="39" t="inlineStr">
         <is>
-          <t>public offer</t>
+          <t>non-public offer</t>
         </is>
       </c>
       <c r="E31" s="39" t="inlineStr">
         <is>
-          <t>INDUSTRY</t>
+          <t>PUBLIC_SECTOR</t>
         </is>
       </c>
       <c r="F31" s="39" t="inlineStr">
         <is>
-          <t>Industry base</t>
+          <t>Government base</t>
         </is>
       </c>
       <c r="G31" s="39" t="inlineStr">
         <is>
-          <t>First Super Pty Limited</t>
+          <t>Fire and Emergency Services Superannuation Board</t>
         </is>
       </c>
       <c r="H31" s="39" t="inlineStr">
         <is>
-          <t>Nominating organisation ownership</t>
+          <t>Public sector organisation ownership</t>
         </is>
       </c>
       <c r="I31" s="39" t="inlineStr">
@@ -13452,43 +13480,43 @@
       </c>
       <c r="J31" s="39" t="inlineStr">
         <is>
-          <t>Equal representation required by governing rules</t>
+          <t>Equal representation required by legislation</t>
         </is>
       </c>
       <c r="K31" s="40" t="n">
-        <v>75700</v>
+        <v>2660</v>
       </c>
       <c r="L31" s="40" t="n">
-        <v>5298429</v>
+        <v>939347</v>
       </c>
       <c r="M31" s="40" t="inlineStr">
         <is>
-          <t>$15,000 to $24,999</t>
+          <t>$200,000 to $499,999</t>
         </is>
       </c>
       <c r="N31" s="40" t="n">
-        <v>24293</v>
+        <v>252882</v>
       </c>
       <c r="O31" s="40" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="P31" s="40" t="n">
-        <v>58800</v>
+        <v>1910</v>
       </c>
       <c r="Q31" s="40" t="n">
-        <v>16900</v>
+        <v>760</v>
       </c>
       <c r="R31" s="40" t="n">
-        <v>4538439</v>
+        <v>654360</v>
       </c>
       <c r="S31" s="40" t="n">
-        <v>759990</v>
+        <v>284988</v>
       </c>
       <c r="T31" s="40" t="n">
-        <v>77.2</v>
+        <v>343.3</v>
       </c>
       <c r="U31" s="40" t="n">
-        <v>45</v>
+        <v>376.5</v>
       </c>
     </row>
     <row r="32" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -13497,11 +13525,11 @@
       </c>
       <c r="B32" s="39" t="inlineStr">
         <is>
-          <t>Guild Retirement Fund</t>
+          <t>First Super</t>
         </is>
       </c>
       <c r="C32" s="39" t="n">
-        <v>22599554834</v>
+        <v>56286625181</v>
       </c>
       <c r="D32" s="39" t="inlineStr">
         <is>
@@ -13510,7 +13538,7 @@
       </c>
       <c r="E32" s="39" t="inlineStr">
         <is>
-          <t>RETAIL</t>
+          <t>INDUSTRY</t>
         </is>
       </c>
       <c r="F32" s="39" t="inlineStr">
@@ -13520,29 +13548,29 @@
       </c>
       <c r="G32" s="39" t="inlineStr">
         <is>
-          <t>Equity Trustees Superannuation Limited</t>
+          <t>First Super Pty Limited</t>
         </is>
       </c>
       <c r="H32" s="39" t="inlineStr">
         <is>
-          <t>Financial services corporation ownership</t>
+          <t>Nominating organisation ownership</t>
         </is>
       </c>
       <c r="I32" s="39" t="inlineStr">
         <is>
-          <t>For profit status</t>
+          <t>Not for profit status</t>
         </is>
       </c>
       <c r="J32" s="39" t="inlineStr">
         <is>
-          <t>Non equal representation</t>
+          <t>Equal representation required by governing rules</t>
         </is>
       </c>
       <c r="K32" s="40" t="n">
-        <v>96880</v>
+        <v>75700</v>
       </c>
       <c r="L32" s="40" t="n">
-        <v>4144122</v>
+        <v>5298429</v>
       </c>
       <c r="M32" s="40" t="inlineStr">
         <is>
@@ -13550,28 +13578,28 @@
         </is>
       </c>
       <c r="N32" s="40" t="n">
-        <v>18032</v>
+        <v>24293</v>
       </c>
       <c r="O32" s="40" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="P32" s="40" t="n">
-        <v>93360</v>
+        <v>58800</v>
       </c>
       <c r="Q32" s="40" t="n">
-        <v>3520</v>
+        <v>16900</v>
       </c>
       <c r="R32" s="40" t="n">
-        <v>4004647</v>
+        <v>4538439</v>
       </c>
       <c r="S32" s="40" t="n">
-        <v>139475</v>
+        <v>759990</v>
       </c>
       <c r="T32" s="40" t="n">
-        <v>42.9</v>
+        <v>77.2</v>
       </c>
       <c r="U32" s="40" t="n">
-        <v>39.6</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -13580,11 +13608,11 @@
       </c>
       <c r="B33" s="39" t="inlineStr">
         <is>
-          <t>HESTA</t>
+          <t>Guild Retirement Fund</t>
         </is>
       </c>
       <c r="C33" s="39" t="n">
-        <v>64971749321</v>
+        <v>22599554834</v>
       </c>
       <c r="D33" s="39" t="inlineStr">
         <is>
@@ -13593,7 +13621,7 @@
       </c>
       <c r="E33" s="39" t="inlineStr">
         <is>
-          <t>INDUSTRY</t>
+          <t>RETAIL</t>
         </is>
       </c>
       <c r="F33" s="39" t="inlineStr">
@@ -13603,58 +13631,58 @@
       </c>
       <c r="G33" s="39" t="inlineStr">
         <is>
-          <t>H.E.S.T. Australia Ltd.</t>
+          <t>Equity Trustees Superannuation Limited</t>
         </is>
       </c>
       <c r="H33" s="39" t="inlineStr">
         <is>
-          <t>Nominating organisation ownership</t>
+          <t>Financial services corporation ownership</t>
         </is>
       </c>
       <c r="I33" s="39" t="inlineStr">
         <is>
-          <t>Not for profit status</t>
+          <t>For profit status</t>
         </is>
       </c>
       <c r="J33" s="39" t="inlineStr">
         <is>
-          <t>Equal representation required by governing rules</t>
+          <t>Non equal representation</t>
         </is>
       </c>
       <c r="K33" s="40" t="n">
-        <v>1092080</v>
+        <v>96880</v>
       </c>
       <c r="L33" s="40" t="n">
-        <v>100966990</v>
+        <v>4144122</v>
       </c>
       <c r="M33" s="40" t="inlineStr">
         <is>
-          <t>$40,000 to $59,999</t>
+          <t>$15,000 to $24,999</t>
         </is>
       </c>
       <c r="N33" s="40" t="n">
-        <v>41823</v>
+        <v>18032</v>
       </c>
       <c r="O33" s="40" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="P33" s="40" t="n">
-        <v>945490</v>
+        <v>93360</v>
       </c>
       <c r="Q33" s="40" t="n">
-        <v>146590</v>
+        <v>3520</v>
       </c>
       <c r="R33" s="40" t="n">
-        <v>92870544</v>
+        <v>4004647</v>
       </c>
       <c r="S33" s="40" t="n">
-        <v>8096446</v>
+        <v>139475</v>
       </c>
       <c r="T33" s="40" t="n">
-        <v>98.2</v>
+        <v>42.9</v>
       </c>
       <c r="U33" s="40" t="n">
-        <v>55.2</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="34" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -13663,11 +13691,11 @@
       </c>
       <c r="B34" s="39" t="inlineStr">
         <is>
-          <t>HOSTPLUS Superannuation Fund</t>
+          <t>HESTA</t>
         </is>
       </c>
       <c r="C34" s="39" t="n">
-        <v>68657495890</v>
+        <v>64971749321</v>
       </c>
       <c r="D34" s="39" t="inlineStr">
         <is>
@@ -13686,7 +13714,7 @@
       </c>
       <c r="G34" s="39" t="inlineStr">
         <is>
-          <t>Host-Plus Pty. Limited</t>
+          <t>H.E.S.T. Australia Ltd.</t>
         </is>
       </c>
       <c r="H34" s="39" t="inlineStr">
@@ -13705,39 +13733,39 @@
         </is>
       </c>
       <c r="K34" s="40" t="n">
-        <v>1919430</v>
+        <v>1092080</v>
       </c>
       <c r="L34" s="40" t="n">
-        <v>144011072</v>
+        <v>100966990</v>
       </c>
       <c r="M34" s="40" t="inlineStr">
         <is>
-          <t>$15,000 to $24,999</t>
+          <t>$40,000 to $59,999</t>
         </is>
       </c>
       <c r="N34" s="40" t="n">
-        <v>24397</v>
+        <v>41823</v>
       </c>
       <c r="O34" s="40" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="P34" s="40" t="n">
-        <v>1629270</v>
+        <v>945490</v>
       </c>
       <c r="Q34" s="40" t="n">
-        <v>290170</v>
+        <v>146590</v>
       </c>
       <c r="R34" s="40" t="n">
-        <v>129519127</v>
+        <v>92870544</v>
       </c>
       <c r="S34" s="40" t="n">
-        <v>14491945</v>
+        <v>8096446</v>
       </c>
       <c r="T34" s="40" t="n">
-        <v>79.5</v>
+        <v>98.2</v>
       </c>
       <c r="U34" s="40" t="n">
-        <v>49.9</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="35" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -13746,11 +13774,11 @@
       </c>
       <c r="B35" s="39" t="inlineStr">
         <is>
-          <t>HUB24 Super Fund</t>
+          <t>HOSTPLUS Superannuation Fund</t>
         </is>
       </c>
       <c r="C35" s="39" t="n">
-        <v>60910190523</v>
+        <v>68657495890</v>
       </c>
       <c r="D35" s="39" t="inlineStr">
         <is>
@@ -13759,68 +13787,68 @@
       </c>
       <c r="E35" s="39" t="inlineStr">
         <is>
-          <t>RETAIL</t>
+          <t>INDUSTRY</t>
         </is>
       </c>
       <c r="F35" s="39" t="inlineStr">
         <is>
-          <t>General base</t>
+          <t>Industry base</t>
         </is>
       </c>
       <c r="G35" s="39" t="inlineStr">
         <is>
-          <t>HTFS Nominees Pty Ltd</t>
+          <t>Host-Plus Pty. Limited</t>
         </is>
       </c>
       <c r="H35" s="39" t="inlineStr">
         <is>
-          <t>Financial services corporation ownership</t>
+          <t>Nominating organisation ownership</t>
         </is>
       </c>
       <c r="I35" s="39" t="inlineStr">
         <is>
-          <t>For profit status</t>
+          <t>Not for profit status</t>
         </is>
       </c>
       <c r="J35" s="39" t="inlineStr">
         <is>
-          <t>Non equal representation</t>
+          <t>Equal representation required by governing rules</t>
         </is>
       </c>
       <c r="K35" s="40" t="n">
-        <v>159930</v>
+        <v>1919430</v>
       </c>
       <c r="L35" s="40" t="n">
-        <v>55330126</v>
+        <v>144011072</v>
       </c>
       <c r="M35" s="40" t="inlineStr">
         <is>
-          <t>$200,000 to $499,999</t>
+          <t>$15,000 to $24,999</t>
         </is>
       </c>
       <c r="N35" s="40" t="n">
-        <v>247995</v>
+        <v>24397</v>
       </c>
       <c r="O35" s="40" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="P35" s="40" t="n">
-        <v>159890</v>
+        <v>1629270</v>
       </c>
       <c r="Q35" s="40" t="n">
-        <v>50</v>
+        <v>290170</v>
       </c>
       <c r="R35" s="40" t="n">
-        <v>55330104</v>
+        <v>129519127</v>
       </c>
       <c r="S35" s="40" t="n">
-        <v>21</v>
+        <v>14491945</v>
       </c>
       <c r="T35" s="40" t="n">
-        <v>346.1</v>
+        <v>79.5</v>
       </c>
       <c r="U35" s="40" t="n">
-        <v>0.5</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="36" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -13829,11 +13857,11 @@
       </c>
       <c r="B36" s="39" t="inlineStr">
         <is>
-          <t>IOOF Portfolio Service Superannuation Fund</t>
+          <t>HUB24 Super Fund</t>
         </is>
       </c>
       <c r="C36" s="39" t="n">
-        <v>70815369818</v>
+        <v>60910190523</v>
       </c>
       <c r="D36" s="39" t="inlineStr">
         <is>
@@ -13852,7 +13880,7 @@
       </c>
       <c r="G36" s="39" t="inlineStr">
         <is>
-          <t>I.O.O.F. Investment Management Limited</t>
+          <t>HTFS Nominees Pty Ltd</t>
         </is>
       </c>
       <c r="H36" s="39" t="inlineStr">
@@ -13871,39 +13899,39 @@
         </is>
       </c>
       <c r="K36" s="40" t="n">
-        <v>277430</v>
+        <v>159930</v>
       </c>
       <c r="L36" s="40" t="n">
-        <v>75895774</v>
+        <v>55330126</v>
       </c>
       <c r="M36" s="40" t="inlineStr">
         <is>
-          <t>$100,000 to $199,999</t>
+          <t>$200,000 to $499,999</t>
         </is>
       </c>
       <c r="N36" s="40" t="n">
-        <v>150650</v>
+        <v>247995</v>
       </c>
       <c r="O36" s="40" t="n">
         <v>60</v>
       </c>
       <c r="P36" s="40" t="n">
-        <v>220560</v>
+        <v>159890</v>
       </c>
       <c r="Q36" s="40" t="n">
-        <v>56870</v>
+        <v>50</v>
       </c>
       <c r="R36" s="40" t="n">
-        <v>67693300</v>
+        <v>55330104</v>
       </c>
       <c r="S36" s="40" t="n">
-        <v>8202474</v>
+        <v>21</v>
       </c>
       <c r="T36" s="40" t="n">
-        <v>306.9</v>
+        <v>346.1</v>
       </c>
       <c r="U36" s="40" t="n">
-        <v>144.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="37" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -13912,11 +13940,11 @@
       </c>
       <c r="B37" s="39" t="inlineStr">
         <is>
-          <t>Lifefocus Superannuation Fund</t>
+          <t>IOOF Portfolio Service Superannuation Fund</t>
         </is>
       </c>
       <c r="C37" s="39" t="n">
-        <v>94579217553</v>
+        <v>70815369818</v>
       </c>
       <c r="D37" s="39" t="inlineStr">
         <is>
@@ -13935,7 +13963,7 @@
       </c>
       <c r="G37" s="39" t="inlineStr">
         <is>
-          <t>CCSL Limited</t>
+          <t>I.O.O.F. Investment Management Limited</t>
         </is>
       </c>
       <c r="H37" s="39" t="inlineStr">
@@ -13954,39 +13982,39 @@
         </is>
       </c>
       <c r="K37" s="40" t="n">
-        <v>20</v>
+        <v>277430</v>
       </c>
       <c r="L37" s="40" t="n">
-        <v>490</v>
+        <v>75895774</v>
       </c>
       <c r="M37" s="40" t="inlineStr">
         <is>
-          <t>&lt;$1,000</t>
+          <t>$100,000 to $199,999</t>
         </is>
       </c>
       <c r="N37" s="40" t="n">
-        <v>325</v>
+        <v>150650</v>
       </c>
       <c r="O37" s="40" t="n">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="P37" s="40" t="n">
-        <v>0</v>
+        <v>220560</v>
       </c>
       <c r="Q37" s="40" t="n">
-        <v>20</v>
+        <v>56870</v>
       </c>
       <c r="R37" s="40" t="n">
-        <v>0</v>
+        <v>67693300</v>
       </c>
       <c r="S37" s="40" t="n">
-        <v>490</v>
+        <v>8202474</v>
       </c>
       <c r="T37" s="40" t="n">
-        <v>0</v>
+        <v>306.9</v>
       </c>
       <c r="U37" s="40" t="n">
-        <v>24.5</v>
+        <v>144.2</v>
       </c>
     </row>
     <row r="38" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -13995,11 +14023,11 @@
       </c>
       <c r="B38" s="39" t="inlineStr">
         <is>
-          <t>Local Authorities Superannuation Fund</t>
+          <t>Lifefocus Superannuation Fund</t>
         </is>
       </c>
       <c r="C38" s="39" t="n">
-        <v>24496637884</v>
+        <v>94579217553</v>
       </c>
       <c r="D38" s="39" t="inlineStr">
         <is>
@@ -14008,68 +14036,68 @@
       </c>
       <c r="E38" s="39" t="inlineStr">
         <is>
-          <t>PUBLIC_SECTOR</t>
+          <t>RETAIL</t>
         </is>
       </c>
       <c r="F38" s="39" t="inlineStr">
         <is>
-          <t>Government base</t>
+          <t>General base</t>
         </is>
       </c>
       <c r="G38" s="39" t="inlineStr">
         <is>
-          <t>Vision Super Pty Ltd</t>
+          <t>CCSL Limited</t>
         </is>
       </c>
       <c r="H38" s="39" t="inlineStr">
         <is>
-          <t>Other ownership type</t>
+          <t>Financial services corporation ownership</t>
         </is>
       </c>
       <c r="I38" s="39" t="inlineStr">
         <is>
-          <t>Not for profit status</t>
+          <t>For profit status</t>
         </is>
       </c>
       <c r="J38" s="39" t="inlineStr">
         <is>
-          <t>Equal representation required by legislation</t>
+          <t>Non equal representation</t>
         </is>
       </c>
       <c r="K38" s="40" t="n">
-        <v>169340</v>
+        <v>20</v>
       </c>
       <c r="L38" s="40" t="n">
-        <v>28803430</v>
+        <v>490</v>
       </c>
       <c r="M38" s="40" t="inlineStr">
         <is>
-          <t>$60,000 to $99,999</t>
+          <t>&lt;$1,000</t>
         </is>
       </c>
       <c r="N38" s="40" t="n">
-        <v>90267</v>
+        <v>325</v>
       </c>
       <c r="O38" s="40" t="n">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="P38" s="40" t="n">
-        <v>149760</v>
+        <v>0</v>
       </c>
       <c r="Q38" s="40" t="n">
-        <v>19580</v>
+        <v>20</v>
       </c>
       <c r="R38" s="40" t="n">
-        <v>27449620</v>
+        <v>0</v>
       </c>
       <c r="S38" s="40" t="n">
-        <v>1353810</v>
+        <v>490</v>
       </c>
       <c r="T38" s="40" t="n">
-        <v>183.3</v>
+        <v>0</v>
       </c>
       <c r="U38" s="40" t="n">
-        <v>69.2</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="39" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -14078,11 +14106,11 @@
       </c>
       <c r="B39" s="39" t="inlineStr">
         <is>
-          <t>MLC Super Fund</t>
+          <t>Local Authorities Superannuation Fund</t>
         </is>
       </c>
       <c r="C39" s="39" t="n">
-        <v>70732426024</v>
+        <v>24496637884</v>
       </c>
       <c r="D39" s="39" t="inlineStr">
         <is>
@@ -14091,39 +14119,39 @@
       </c>
       <c r="E39" s="39" t="inlineStr">
         <is>
-          <t>RETAIL</t>
+          <t>PUBLIC_SECTOR</t>
         </is>
       </c>
       <c r="F39" s="39" t="inlineStr">
         <is>
-          <t>General base</t>
+          <t>Government base</t>
         </is>
       </c>
       <c r="G39" s="39" t="inlineStr">
         <is>
-          <t>Nulis Nominees (Australia) Limited</t>
+          <t>Vision Super Pty Ltd</t>
         </is>
       </c>
       <c r="H39" s="39" t="inlineStr">
         <is>
-          <t>Financial services corporation ownership</t>
+          <t>Other ownership type</t>
         </is>
       </c>
       <c r="I39" s="39" t="inlineStr">
         <is>
-          <t>For profit status</t>
+          <t>Not for profit status</t>
         </is>
       </c>
       <c r="J39" s="39" t="inlineStr">
         <is>
-          <t>Non equal representation</t>
+          <t>Equal representation required by legislation</t>
         </is>
       </c>
       <c r="K39" s="40" t="n">
-        <v>637200</v>
+        <v>169340</v>
       </c>
       <c r="L39" s="40" t="n">
-        <v>94575596</v>
+        <v>28803430</v>
       </c>
       <c r="M39" s="40" t="inlineStr">
         <is>
@@ -14131,28 +14159,28 @@
         </is>
       </c>
       <c r="N39" s="40" t="n">
-        <v>63999</v>
+        <v>90267</v>
       </c>
       <c r="O39" s="40" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="P39" s="40" t="n">
-        <v>446260</v>
+        <v>149760</v>
       </c>
       <c r="Q39" s="40" t="n">
-        <v>190940</v>
+        <v>19580</v>
       </c>
       <c r="R39" s="40" t="n">
-        <v>76906099</v>
+        <v>27449620</v>
       </c>
       <c r="S39" s="40" t="n">
-        <v>17669497</v>
+        <v>1353810</v>
       </c>
       <c r="T39" s="40" t="n">
-        <v>172.3</v>
+        <v>183.3</v>
       </c>
       <c r="U39" s="40" t="n">
-        <v>92.5</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="40" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -14161,11 +14189,11 @@
       </c>
       <c r="B40" s="39" t="inlineStr">
         <is>
-          <t>Macquarie Superannuation Plan</t>
+          <t>MLC Super Fund</t>
         </is>
       </c>
       <c r="C40" s="39" t="n">
-        <v>65508799106</v>
+        <v>70732426024</v>
       </c>
       <c r="D40" s="39" t="inlineStr">
         <is>
@@ -14184,7 +14212,7 @@
       </c>
       <c r="G40" s="39" t="inlineStr">
         <is>
-          <t>Macquarie Investment Management Ltd</t>
+          <t>Nulis Nominees (Australia) Limited</t>
         </is>
       </c>
       <c r="H40" s="39" t="inlineStr">
@@ -14203,39 +14231,39 @@
         </is>
       </c>
       <c r="K40" s="40" t="n">
-        <v>123210</v>
+        <v>637200</v>
       </c>
       <c r="L40" s="40" t="n">
-        <v>51206796</v>
+        <v>94575596</v>
       </c>
       <c r="M40" s="40" t="inlineStr">
         <is>
-          <t>$200,000 to $499,999</t>
+          <t>$60,000 to $99,999</t>
         </is>
       </c>
       <c r="N40" s="40" t="n">
-        <v>299269</v>
+        <v>63999</v>
       </c>
       <c r="O40" s="40" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="P40" s="40" t="n">
-        <v>109870</v>
+        <v>446260</v>
       </c>
       <c r="Q40" s="40" t="n">
-        <v>13330</v>
+        <v>190940</v>
       </c>
       <c r="R40" s="40" t="n">
-        <v>47319309</v>
+        <v>76906099</v>
       </c>
       <c r="S40" s="40" t="n">
-        <v>3887486</v>
+        <v>17669497</v>
       </c>
       <c r="T40" s="40" t="n">
-        <v>430.7</v>
+        <v>172.3</v>
       </c>
       <c r="U40" s="40" t="n">
-        <v>291.6</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="41" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -14244,15 +14272,15 @@
       </c>
       <c r="B41" s="39" t="inlineStr">
         <is>
-          <t>Macquarie University Professorial Superannuation Scheme</t>
+          <t>Macquarie Superannuation Plan</t>
         </is>
       </c>
       <c r="C41" s="39" t="n">
-        <v>98415348576</v>
+        <v>65508799106</v>
       </c>
       <c r="D41" s="39" t="inlineStr">
         <is>
-          <t>non-public offer</t>
+          <t>public offer</t>
         </is>
       </c>
       <c r="E41" s="39" t="inlineStr">
@@ -14267,7 +14295,7 @@
       </c>
       <c r="G41" s="39" t="inlineStr">
         <is>
-          <t>Diversa Trustees Limited</t>
+          <t>Macquarie Investment Management Ltd</t>
         </is>
       </c>
       <c r="H41" s="39" t="inlineStr">
@@ -14285,60 +14313,40 @@
           <t>Non equal representation</t>
         </is>
       </c>
-      <c r="K41" s="40" t="inlineStr">
-        <is>
-          <t>&lt;20</t>
-        </is>
-      </c>
-      <c r="L41" s="40" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
+      <c r="K41" s="40" t="n">
+        <v>123210</v>
+      </c>
+      <c r="L41" s="40" t="n">
+        <v>51206796</v>
       </c>
       <c r="M41" s="40" t="inlineStr">
         <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="N41" s="40" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="O41" s="40" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="P41" s="40" t="inlineStr">
-        <is>
-          <t>&lt;20</t>
-        </is>
-      </c>
-      <c r="Q41" s="40" t="inlineStr">
-        <is>
-          <t>&lt;20</t>
-        </is>
-      </c>
-      <c r="R41" s="40" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="S41" s="40" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="T41" s="40" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="U41" s="40" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
+          <t>$200,000 to $499,999</t>
+        </is>
+      </c>
+      <c r="N41" s="40" t="n">
+        <v>299269</v>
+      </c>
+      <c r="O41" s="40" t="n">
+        <v>63</v>
+      </c>
+      <c r="P41" s="40" t="n">
+        <v>109870</v>
+      </c>
+      <c r="Q41" s="40" t="n">
+        <v>13330</v>
+      </c>
+      <c r="R41" s="40" t="n">
+        <v>47319309</v>
+      </c>
+      <c r="S41" s="40" t="n">
+        <v>3887486</v>
+      </c>
+      <c r="T41" s="40" t="n">
+        <v>430.7</v>
+      </c>
+      <c r="U41" s="40" t="n">
+        <v>291.6</v>
       </c>
     </row>
     <row r="42" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -14347,15 +14355,15 @@
       </c>
       <c r="B42" s="39" t="inlineStr">
         <is>
-          <t>Mason Stevens Super</t>
+          <t>Macquarie University Professorial Superannuation Scheme</t>
         </is>
       </c>
       <c r="C42" s="39" t="n">
-        <v>34422545198</v>
+        <v>98415348576</v>
       </c>
       <c r="D42" s="39" t="inlineStr">
         <is>
-          <t>public offer</t>
+          <t>non-public offer</t>
         </is>
       </c>
       <c r="E42" s="39" t="inlineStr">
@@ -14388,40 +14396,60 @@
           <t>Non equal representation</t>
         </is>
       </c>
-      <c r="K42" s="40" t="n">
-        <v>3550</v>
-      </c>
-      <c r="L42" s="40" t="n">
-        <v>1358193</v>
+      <c r="K42" s="40" t="inlineStr">
+        <is>
+          <t>&lt;20</t>
+        </is>
+      </c>
+      <c r="L42" s="40" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
       </c>
       <c r="M42" s="40" t="inlineStr">
         <is>
-          <t>$200,000 to $499,999</t>
-        </is>
-      </c>
-      <c r="N42" s="40" t="n">
-        <v>302427</v>
-      </c>
-      <c r="O42" s="40" t="n">
-        <v>64</v>
-      </c>
-      <c r="P42" s="40" t="n">
-        <v>3170</v>
-      </c>
-      <c r="Q42" s="40" t="n">
-        <v>380</v>
-      </c>
-      <c r="R42" s="40" t="n">
-        <v>1259427</v>
-      </c>
-      <c r="S42" s="40" t="n">
-        <v>98766</v>
-      </c>
-      <c r="T42" s="40" t="n">
-        <v>397.5</v>
-      </c>
-      <c r="U42" s="40" t="n">
-        <v>260.6</v>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="N42" s="40" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="O42" s="40" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="P42" s="40" t="inlineStr">
+        <is>
+          <t>&lt;20</t>
+        </is>
+      </c>
+      <c r="Q42" s="40" t="inlineStr">
+        <is>
+          <t>&lt;20</t>
+        </is>
+      </c>
+      <c r="R42" s="40" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="S42" s="40" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="T42" s="40" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="U42" s="40" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
       </c>
     </row>
     <row r="43" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -14430,11 +14458,11 @@
       </c>
       <c r="B43" s="39" t="inlineStr">
         <is>
-          <t>Mercer Super Trust</t>
+          <t>Mason Stevens Super</t>
         </is>
       </c>
       <c r="C43" s="39" t="n">
-        <v>19905422981</v>
+        <v>34422545198</v>
       </c>
       <c r="D43" s="39" t="inlineStr">
         <is>
@@ -14448,12 +14476,12 @@
       </c>
       <c r="F43" s="39" t="inlineStr">
         <is>
-          <t>Corporate base</t>
+          <t>General base</t>
         </is>
       </c>
       <c r="G43" s="39" t="inlineStr">
         <is>
-          <t>Mercer Superannuation (Australia) Limited</t>
+          <t>Diversa Trustees Limited</t>
         </is>
       </c>
       <c r="H43" s="39" t="inlineStr">
@@ -14472,39 +14500,39 @@
         </is>
       </c>
       <c r="K43" s="40" t="n">
-        <v>1024530</v>
+        <v>3550</v>
       </c>
       <c r="L43" s="40" t="n">
-        <v>82150990</v>
+        <v>1358193</v>
       </c>
       <c r="M43" s="40" t="inlineStr">
         <is>
-          <t>$10,000 to $14,999</t>
+          <t>$200,000 to $499,999</t>
         </is>
       </c>
       <c r="N43" s="40" t="n">
-        <v>12778</v>
+        <v>302427</v>
       </c>
       <c r="O43" s="40" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="P43" s="40" t="n">
-        <v>780750</v>
+        <v>3170</v>
       </c>
       <c r="Q43" s="40" t="n">
-        <v>243780</v>
+        <v>380</v>
       </c>
       <c r="R43" s="40" t="n">
-        <v>66713440</v>
+        <v>1259427</v>
       </c>
       <c r="S43" s="40" t="n">
-        <v>15437550</v>
+        <v>98766</v>
       </c>
       <c r="T43" s="40" t="n">
-        <v>85.40000000000001</v>
+        <v>397.5</v>
       </c>
       <c r="U43" s="40" t="n">
-        <v>63.3</v>
+        <v>260.6</v>
       </c>
     </row>
     <row r="44" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -14513,81 +14541,81 @@
       </c>
       <c r="B44" s="39" t="inlineStr">
         <is>
-          <t>Military Superannuation &amp; Benefits Fund No 1</t>
+          <t>Mercer Super Trust</t>
         </is>
       </c>
       <c r="C44" s="39" t="n">
-        <v>50925523120</v>
+        <v>19905422981</v>
       </c>
       <c r="D44" s="39" t="inlineStr">
         <is>
-          <t>non-public offer</t>
+          <t>public offer</t>
         </is>
       </c>
       <c r="E44" s="39" t="inlineStr">
         <is>
-          <t>PUBLIC_SECTOR</t>
+          <t>RETAIL</t>
         </is>
       </c>
       <c r="F44" s="39" t="inlineStr">
         <is>
-          <t>Government base</t>
+          <t>Corporate base</t>
         </is>
       </c>
       <c r="G44" s="39" t="inlineStr">
         <is>
-          <t>Commonwealth Superannuation Corporation</t>
+          <t>Mercer Superannuation (Australia) Limited</t>
         </is>
       </c>
       <c r="H44" s="39" t="inlineStr">
         <is>
-          <t>Public sector organisation ownership</t>
+          <t>Financial services corporation ownership</t>
         </is>
       </c>
       <c r="I44" s="39" t="inlineStr">
         <is>
-          <t>Not for profit status</t>
+          <t>For profit status</t>
         </is>
       </c>
       <c r="J44" s="39" t="inlineStr">
         <is>
-          <t>Equal representation required by legislation</t>
+          <t>Non equal representation</t>
         </is>
       </c>
       <c r="K44" s="40" t="n">
-        <v>182490</v>
+        <v>1024530</v>
       </c>
       <c r="L44" s="40" t="n">
-        <v>99764000</v>
+        <v>82150990</v>
       </c>
       <c r="M44" s="40" t="inlineStr">
         <is>
-          <t>$500,000 to $999,999</t>
+          <t>$10,000 to $14,999</t>
         </is>
       </c>
       <c r="N44" s="40" t="n">
-        <v>550879</v>
+        <v>12778</v>
       </c>
       <c r="O44" s="40" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="P44" s="40" t="n">
-        <v>182490</v>
+        <v>780750</v>
       </c>
       <c r="Q44" s="40" t="n">
-        <v>0</v>
+        <v>243780</v>
       </c>
       <c r="R44" s="40" t="n">
-        <v>99764000</v>
+        <v>66713440</v>
       </c>
       <c r="S44" s="40" t="n">
-        <v>0</v>
+        <v>15437550</v>
       </c>
       <c r="T44" s="40" t="n">
-        <v>546.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="U44" s="40" t="n">
-        <v>0</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="45" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -14596,35 +14624,35 @@
       </c>
       <c r="B45" s="39" t="inlineStr">
         <is>
-          <t>NESS Super</t>
+          <t>Military Superannuation &amp; Benefits Fund No 1</t>
         </is>
       </c>
       <c r="C45" s="39" t="n">
-        <v>72229227691</v>
+        <v>50925523120</v>
       </c>
       <c r="D45" s="39" t="inlineStr">
         <is>
-          <t>public offer</t>
+          <t>non-public offer</t>
         </is>
       </c>
       <c r="E45" s="39" t="inlineStr">
         <is>
-          <t>INDUSTRY</t>
+          <t>PUBLIC_SECTOR</t>
         </is>
       </c>
       <c r="F45" s="39" t="inlineStr">
         <is>
-          <t>Industry base</t>
+          <t>Government base</t>
         </is>
       </c>
       <c r="G45" s="39" t="inlineStr">
         <is>
-          <t>NESS Super Pty Ltd</t>
+          <t>Commonwealth Superannuation Corporation</t>
         </is>
       </c>
       <c r="H45" s="39" t="inlineStr">
         <is>
-          <t>Nominating organisation ownership</t>
+          <t>Public sector organisation ownership</t>
         </is>
       </c>
       <c r="I45" s="39" t="inlineStr">
@@ -14634,43 +14662,43 @@
       </c>
       <c r="J45" s="39" t="inlineStr">
         <is>
-          <t>Equal representation required by governing rules</t>
+          <t>Equal representation required by legislation</t>
         </is>
       </c>
       <c r="K45" s="40" t="n">
-        <v>13340</v>
+        <v>182490</v>
       </c>
       <c r="L45" s="40" t="n">
-        <v>1358209</v>
+        <v>99764000</v>
       </c>
       <c r="M45" s="40" t="inlineStr">
         <is>
-          <t>$40,000 to $59,999</t>
+          <t>$500,000 to $999,999</t>
         </is>
       </c>
       <c r="N45" s="40" t="n">
-        <v>46224</v>
+        <v>550879</v>
       </c>
       <c r="O45" s="40" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="P45" s="40" t="n">
-        <v>10660</v>
+        <v>182490</v>
       </c>
       <c r="Q45" s="40" t="n">
-        <v>2680</v>
+        <v>0</v>
       </c>
       <c r="R45" s="40" t="n">
-        <v>1220357</v>
+        <v>99764000</v>
       </c>
       <c r="S45" s="40" t="n">
-        <v>137852</v>
+        <v>0</v>
       </c>
       <c r="T45" s="40" t="n">
-        <v>114.5</v>
+        <v>546.7</v>
       </c>
       <c r="U45" s="40" t="n">
-        <v>51.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -14679,11 +14707,11 @@
       </c>
       <c r="B46" s="39" t="inlineStr">
         <is>
-          <t>NGS Super</t>
+          <t>NESS Super</t>
         </is>
       </c>
       <c r="C46" s="39" t="n">
-        <v>73549180515</v>
+        <v>72229227691</v>
       </c>
       <c r="D46" s="39" t="inlineStr">
         <is>
@@ -14702,12 +14730,12 @@
       </c>
       <c r="G46" s="39" t="inlineStr">
         <is>
-          <t>NGS Super Pty Limited</t>
+          <t>NESS Super Pty Ltd</t>
         </is>
       </c>
       <c r="H46" s="39" t="inlineStr">
         <is>
-          <t>Financial services corporation ownership</t>
+          <t>Nominating organisation ownership</t>
         </is>
       </c>
       <c r="I46" s="39" t="inlineStr">
@@ -14721,39 +14749,39 @@
         </is>
       </c>
       <c r="K46" s="40" t="n">
-        <v>110210</v>
+        <v>13340</v>
       </c>
       <c r="L46" s="40" t="n">
-        <v>17372003</v>
+        <v>1358209</v>
       </c>
       <c r="M46" s="40" t="inlineStr">
         <is>
-          <t>$60,000 to $99,999</t>
+          <t>$40,000 to $59,999</t>
         </is>
       </c>
       <c r="N46" s="40" t="n">
-        <v>66331</v>
+        <v>46224</v>
       </c>
       <c r="O46" s="40" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="P46" s="40" t="n">
-        <v>90570</v>
+        <v>10660</v>
       </c>
       <c r="Q46" s="40" t="n">
-        <v>19640</v>
+        <v>2680</v>
       </c>
       <c r="R46" s="40" t="n">
-        <v>15635329</v>
+        <v>1220357</v>
       </c>
       <c r="S46" s="40" t="n">
-        <v>1736674</v>
+        <v>137852</v>
       </c>
       <c r="T46" s="40" t="n">
-        <v>172.6</v>
+        <v>114.5</v>
       </c>
       <c r="U46" s="40" t="n">
-        <v>88.40000000000001</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="47" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -14762,11 +14790,11 @@
       </c>
       <c r="B47" s="39" t="inlineStr">
         <is>
-          <t>National Mutual Retirement Fund</t>
+          <t>NGS Super</t>
         </is>
       </c>
       <c r="C47" s="39" t="n">
-        <v>76746741299</v>
+        <v>73549180515</v>
       </c>
       <c r="D47" s="39" t="inlineStr">
         <is>
@@ -14775,17 +14803,17 @@
       </c>
       <c r="E47" s="39" t="inlineStr">
         <is>
-          <t>RETAIL</t>
+          <t>INDUSTRY</t>
         </is>
       </c>
       <c r="F47" s="39" t="inlineStr">
         <is>
-          <t>General base</t>
+          <t>Industry base</t>
         </is>
       </c>
       <c r="G47" s="39" t="inlineStr">
         <is>
-          <t>Equity Trustees Superannuation Limited</t>
+          <t>NGS Super Pty Limited</t>
         </is>
       </c>
       <c r="H47" s="39" t="inlineStr">
@@ -14795,48 +14823,48 @@
       </c>
       <c r="I47" s="39" t="inlineStr">
         <is>
-          <t>For profit status</t>
+          <t>Not for profit status</t>
         </is>
       </c>
       <c r="J47" s="39" t="inlineStr">
         <is>
-          <t>Non equal representation</t>
+          <t>Equal representation required by governing rules</t>
         </is>
       </c>
       <c r="K47" s="40" t="n">
-        <v>136630</v>
+        <v>110210</v>
       </c>
       <c r="L47" s="40" t="n">
-        <v>5618625</v>
+        <v>17372003</v>
       </c>
       <c r="M47" s="40" t="inlineStr">
         <is>
-          <t>$15,000 to $24,999</t>
+          <t>$60,000 to $99,999</t>
         </is>
       </c>
       <c r="N47" s="40" t="n">
-        <v>16394</v>
+        <v>66331</v>
       </c>
       <c r="O47" s="40" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="P47" s="40" t="n">
-        <v>58530</v>
+        <v>90570</v>
       </c>
       <c r="Q47" s="40" t="n">
-        <v>78110</v>
+        <v>19640</v>
       </c>
       <c r="R47" s="40" t="n">
-        <v>3189470</v>
+        <v>15635329</v>
       </c>
       <c r="S47" s="40" t="n">
-        <v>2429155</v>
+        <v>1736674</v>
       </c>
       <c r="T47" s="40" t="n">
-        <v>54.5</v>
+        <v>172.6</v>
       </c>
       <c r="U47" s="40" t="n">
-        <v>31.1</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="48" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -14845,11 +14873,11 @@
       </c>
       <c r="B48" s="39" t="inlineStr">
         <is>
-          <t>Netwealth Superannuation Master Fund</t>
+          <t>National Mutual Retirement Fund</t>
         </is>
       </c>
       <c r="C48" s="39" t="n">
-        <v>94573747704</v>
+        <v>76746741299</v>
       </c>
       <c r="D48" s="39" t="inlineStr">
         <is>
@@ -14868,7 +14896,7 @@
       </c>
       <c r="G48" s="39" t="inlineStr">
         <is>
-          <t>Netwealth Superannuation Services Pty Ltd</t>
+          <t>Equity Trustees Superannuation Limited</t>
         </is>
       </c>
       <c r="H48" s="39" t="inlineStr">
@@ -14887,39 +14915,39 @@
         </is>
       </c>
       <c r="K48" s="40" t="n">
-        <v>117570</v>
+        <v>136630</v>
       </c>
       <c r="L48" s="40" t="n">
-        <v>41590986</v>
+        <v>5618625</v>
       </c>
       <c r="M48" s="40" t="inlineStr">
         <is>
-          <t>$200,000 to $499,999</t>
+          <t>$15,000 to $24,999</t>
         </is>
       </c>
       <c r="N48" s="40" t="n">
-        <v>245612</v>
+        <v>16394</v>
       </c>
       <c r="O48" s="40" t="n">
         <v>60</v>
       </c>
       <c r="P48" s="40" t="n">
-        <v>103950</v>
+        <v>58530</v>
       </c>
       <c r="Q48" s="40" t="n">
-        <v>13620</v>
+        <v>78110</v>
       </c>
       <c r="R48" s="40" t="n">
-        <v>38678088</v>
+        <v>3189470</v>
       </c>
       <c r="S48" s="40" t="n">
-        <v>2912898</v>
+        <v>2429155</v>
       </c>
       <c r="T48" s="40" t="n">
-        <v>372.1</v>
+        <v>54.5</v>
       </c>
       <c r="U48" s="40" t="n">
-        <v>213.9</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="49" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -14928,11 +14956,11 @@
       </c>
       <c r="B49" s="39" t="inlineStr">
         <is>
-          <t>Oasis Superannuation Master Trust</t>
+          <t>Netwealth Superannuation Master Fund</t>
         </is>
       </c>
       <c r="C49" s="39" t="n">
-        <v>81154851339</v>
+        <v>94573747704</v>
       </c>
       <c r="D49" s="39" t="inlineStr">
         <is>
@@ -14951,7 +14979,7 @@
       </c>
       <c r="G49" s="39" t="inlineStr">
         <is>
-          <t>Oasis Fund Management Limited</t>
+          <t>Netwealth Superannuation Services Pty Ltd</t>
         </is>
       </c>
       <c r="H49" s="39" t="inlineStr">
@@ -14970,39 +14998,39 @@
         </is>
       </c>
       <c r="K49" s="40" t="n">
-        <v>11230</v>
+        <v>117570</v>
       </c>
       <c r="L49" s="40" t="n">
-        <v>2361371</v>
+        <v>41590986</v>
       </c>
       <c r="M49" s="40" t="inlineStr">
         <is>
-          <t>$60,000 to $99,999</t>
+          <t>$200,000 to $499,999</t>
         </is>
       </c>
       <c r="N49" s="40" t="n">
-        <v>93779</v>
+        <v>245612</v>
       </c>
       <c r="O49" s="40" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="P49" s="40" t="n">
-        <v>7610</v>
+        <v>103950</v>
       </c>
       <c r="Q49" s="40" t="n">
-        <v>3620</v>
+        <v>13620</v>
       </c>
       <c r="R49" s="40" t="n">
-        <v>2040057</v>
+        <v>38678088</v>
       </c>
       <c r="S49" s="40" t="n">
-        <v>321314</v>
+        <v>2912898</v>
       </c>
       <c r="T49" s="40" t="n">
-        <v>268</v>
+        <v>372.1</v>
       </c>
       <c r="U49" s="40" t="n">
-        <v>88.8</v>
+        <v>213.9</v>
       </c>
     </row>
     <row r="50" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -15011,11 +15039,11 @@
       </c>
       <c r="B50" s="39" t="inlineStr">
         <is>
-          <t>OneSuper</t>
+          <t>Oasis Superannuation Master Trust</t>
         </is>
       </c>
       <c r="C50" s="39" t="n">
-        <v>43905581638</v>
+        <v>81154851339</v>
       </c>
       <c r="D50" s="39" t="inlineStr">
         <is>
@@ -15034,7 +15062,7 @@
       </c>
       <c r="G50" s="39" t="inlineStr">
         <is>
-          <t>Diversa Trustees Limited</t>
+          <t>Oasis Fund Management Limited</t>
         </is>
       </c>
       <c r="H50" s="39" t="inlineStr">
@@ -15053,39 +15081,39 @@
         </is>
       </c>
       <c r="K50" s="40" t="n">
-        <v>232330</v>
+        <v>11230</v>
       </c>
       <c r="L50" s="40" t="n">
-        <v>7826801</v>
+        <v>2361371</v>
       </c>
       <c r="M50" s="40" t="inlineStr">
         <is>
-          <t>$1,000 to $5,999</t>
+          <t>$60,000 to $99,999</t>
         </is>
       </c>
       <c r="N50" s="40" t="n">
-        <v>5748</v>
+        <v>93779</v>
       </c>
       <c r="O50" s="40" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="P50" s="40" t="n">
-        <v>211670</v>
+        <v>7610</v>
       </c>
       <c r="Q50" s="40" t="n">
-        <v>20660</v>
+        <v>3620</v>
       </c>
       <c r="R50" s="40" t="n">
-        <v>7237593</v>
+        <v>2040057</v>
       </c>
       <c r="S50" s="40" t="n">
-        <v>589208</v>
+        <v>321314</v>
       </c>
       <c r="T50" s="40" t="n">
-        <v>34.2</v>
+        <v>268</v>
       </c>
       <c r="U50" s="40" t="n">
-        <v>28.5</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="51" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -15094,11 +15122,11 @@
       </c>
       <c r="B51" s="39" t="inlineStr">
         <is>
-          <t>Perpetual Super Wrap</t>
+          <t>OneSuper</t>
         </is>
       </c>
       <c r="C51" s="39" t="n">
-        <v>22897174641</v>
+        <v>43905581638</v>
       </c>
       <c r="D51" s="39" t="inlineStr">
         <is>
@@ -15117,7 +15145,7 @@
       </c>
       <c r="G51" s="39" t="inlineStr">
         <is>
-          <t>Equity Trustees Superannuation Limited</t>
+          <t>Diversa Trustees Limited</t>
         </is>
       </c>
       <c r="H51" s="39" t="inlineStr">
@@ -15136,39 +15164,39 @@
         </is>
       </c>
       <c r="K51" s="40" t="n">
-        <v>4030</v>
+        <v>232330</v>
       </c>
       <c r="L51" s="40" t="n">
-        <v>3134553</v>
+        <v>7826801</v>
       </c>
       <c r="M51" s="40" t="inlineStr">
         <is>
-          <t>$200,000 to $499,999</t>
+          <t>$1,000 to $5,999</t>
         </is>
       </c>
       <c r="N51" s="40" t="n">
-        <v>439444</v>
+        <v>5748</v>
       </c>
       <c r="O51" s="40" t="n">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="P51" s="40" t="n">
-        <v>3670</v>
+        <v>211670</v>
       </c>
       <c r="Q51" s="40" t="n">
-        <v>360</v>
+        <v>20660</v>
       </c>
       <c r="R51" s="40" t="n">
-        <v>2965387</v>
+        <v>7237593</v>
       </c>
       <c r="S51" s="40" t="n">
-        <v>169165</v>
+        <v>589208</v>
       </c>
       <c r="T51" s="40" t="n">
-        <v>808.2</v>
+        <v>34.2</v>
       </c>
       <c r="U51" s="40" t="n">
-        <v>472.5</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="52" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -15177,11 +15205,11 @@
       </c>
       <c r="B52" s="39" t="inlineStr">
         <is>
-          <t>Perpetual WealthFocus Superannuation Fund</t>
+          <t>Perpetual Super Wrap</t>
         </is>
       </c>
       <c r="C52" s="39" t="n">
-        <v>41772007500</v>
+        <v>22897174641</v>
       </c>
       <c r="D52" s="39" t="inlineStr">
         <is>
@@ -15219,39 +15247,39 @@
         </is>
       </c>
       <c r="K52" s="40" t="n">
-        <v>7590</v>
+        <v>4030</v>
       </c>
       <c r="L52" s="40" t="n">
-        <v>1467236</v>
+        <v>3134553</v>
       </c>
       <c r="M52" s="40" t="inlineStr">
         <is>
-          <t>$100,000 to $199,999</t>
+          <t>$200,000 to $499,999</t>
         </is>
       </c>
       <c r="N52" s="40" t="n">
-        <v>111682</v>
+        <v>439444</v>
       </c>
       <c r="O52" s="40" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="P52" s="40" t="n">
-        <v>4760</v>
+        <v>3670</v>
       </c>
       <c r="Q52" s="40" t="n">
-        <v>2830</v>
+        <v>360</v>
       </c>
       <c r="R52" s="40" t="n">
-        <v>1001791</v>
+        <v>2965387</v>
       </c>
       <c r="S52" s="40" t="n">
-        <v>465445</v>
+        <v>169165</v>
       </c>
       <c r="T52" s="40" t="n">
-        <v>210.6</v>
+        <v>808.2</v>
       </c>
       <c r="U52" s="40" t="n">
-        <v>164.5</v>
+        <v>472.5</v>
       </c>
     </row>
     <row r="53" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -15260,11 +15288,11 @@
       </c>
       <c r="B53" s="39" t="inlineStr">
         <is>
-          <t>Perpetual's Select Superannuation Fund</t>
+          <t>Perpetual WealthFocus Superannuation Fund</t>
         </is>
       </c>
       <c r="C53" s="39" t="n">
-        <v>51068260563</v>
+        <v>41772007500</v>
       </c>
       <c r="D53" s="39" t="inlineStr">
         <is>
@@ -15302,10 +15330,10 @@
         </is>
       </c>
       <c r="K53" s="40" t="n">
-        <v>3700</v>
+        <v>7590</v>
       </c>
       <c r="L53" s="40" t="n">
-        <v>1109687</v>
+        <v>1467236</v>
       </c>
       <c r="M53" s="40" t="inlineStr">
         <is>
@@ -15313,28 +15341,28 @@
         </is>
       </c>
       <c r="N53" s="40" t="n">
-        <v>135817</v>
+        <v>111682</v>
       </c>
       <c r="O53" s="40" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="P53" s="40" t="n">
-        <v>2250</v>
+        <v>4760</v>
       </c>
       <c r="Q53" s="40" t="n">
-        <v>1450</v>
+        <v>2830</v>
       </c>
       <c r="R53" s="40" t="n">
-        <v>884570</v>
+        <v>1001791</v>
       </c>
       <c r="S53" s="40" t="n">
-        <v>225117</v>
+        <v>465445</v>
       </c>
       <c r="T53" s="40" t="n">
-        <v>393.3</v>
+        <v>210.6</v>
       </c>
       <c r="U53" s="40" t="n">
-        <v>154.8</v>
+        <v>164.5</v>
       </c>
     </row>
     <row r="54" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -15343,11 +15371,11 @@
       </c>
       <c r="B54" s="39" t="inlineStr">
         <is>
-          <t>Personal Choice Private Fund</t>
+          <t>Perpetual's Select Superannuation Fund</t>
         </is>
       </c>
       <c r="C54" s="39" t="n">
-        <v>50159477169</v>
+        <v>51068260563</v>
       </c>
       <c r="D54" s="39" t="inlineStr">
         <is>
@@ -15366,7 +15394,7 @@
       </c>
       <c r="G54" s="39" t="inlineStr">
         <is>
-          <t>CCSL Limited</t>
+          <t>Equity Trustees Superannuation Limited</t>
         </is>
       </c>
       <c r="H54" s="39" t="inlineStr">
@@ -15385,39 +15413,39 @@
         </is>
       </c>
       <c r="K54" s="40" t="n">
-        <v>40</v>
+        <v>3700</v>
       </c>
       <c r="L54" s="40" t="n">
-        <v>15</v>
+        <v>1109687</v>
       </c>
       <c r="M54" s="40" t="inlineStr">
         <is>
-          <t>&lt;$1,000</t>
+          <t>$100,000 to $199,999</t>
         </is>
       </c>
       <c r="N54" s="40" t="n">
-        <v>327</v>
+        <v>135817</v>
       </c>
       <c r="O54" s="40" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="P54" s="40" t="n">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="Q54" s="40" t="n">
-        <v>40</v>
+        <v>1450</v>
       </c>
       <c r="R54" s="40" t="n">
-        <v>0</v>
+        <v>884570</v>
       </c>
       <c r="S54" s="40" t="n">
-        <v>15</v>
+        <v>225117</v>
       </c>
       <c r="T54" s="40" t="n">
-        <v>0</v>
+        <v>393.3</v>
       </c>
       <c r="U54" s="40" t="n">
-        <v>0.4</v>
+        <v>154.8</v>
       </c>
     </row>
     <row r="55" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -15426,11 +15454,11 @@
       </c>
       <c r="B55" s="39" t="inlineStr">
         <is>
-          <t>Praemium SMA Superannuation Fund</t>
+          <t>Personal Choice Private Fund</t>
         </is>
       </c>
       <c r="C55" s="39" t="n">
-        <v>75703857864</v>
+        <v>50159477169</v>
       </c>
       <c r="D55" s="39" t="inlineStr">
         <is>
@@ -15449,7 +15477,7 @@
       </c>
       <c r="G55" s="39" t="inlineStr">
         <is>
-          <t>Diversa Trustees Limited</t>
+          <t>CCSL Limited</t>
         </is>
       </c>
       <c r="H55" s="39" t="inlineStr">
@@ -15468,39 +15496,39 @@
         </is>
       </c>
       <c r="K55" s="40" t="n">
-        <v>15280</v>
+        <v>40</v>
       </c>
       <c r="L55" s="40" t="n">
-        <v>5452754</v>
+        <v>15</v>
       </c>
       <c r="M55" s="40" t="inlineStr">
         <is>
-          <t>$200,000 to $499,999</t>
+          <t>&lt;$1,000</t>
         </is>
       </c>
       <c r="N55" s="40" t="n">
-        <v>273087</v>
+        <v>327</v>
       </c>
       <c r="O55" s="40" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="P55" s="40" t="n">
-        <v>15200</v>
+        <v>0</v>
       </c>
       <c r="Q55" s="40" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="R55" s="40" t="n">
-        <v>5450124</v>
+        <v>0</v>
       </c>
       <c r="S55" s="40" t="n">
-        <v>2630</v>
+        <v>15</v>
       </c>
       <c r="T55" s="40" t="n">
-        <v>358.7</v>
+        <v>0</v>
       </c>
       <c r="U55" s="40" t="n">
-        <v>31.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="56" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -15509,11 +15537,11 @@
       </c>
       <c r="B56" s="39" t="inlineStr">
         <is>
-          <t>Prime Super</t>
+          <t>Praemium SMA Superannuation Fund</t>
         </is>
       </c>
       <c r="C56" s="39" t="n">
-        <v>60562335823</v>
+        <v>75703857864</v>
       </c>
       <c r="D56" s="39" t="inlineStr">
         <is>
@@ -15522,27 +15550,27 @@
       </c>
       <c r="E56" s="39" t="inlineStr">
         <is>
-          <t>INDUSTRY</t>
+          <t>RETAIL</t>
         </is>
       </c>
       <c r="F56" s="39" t="inlineStr">
         <is>
-          <t>Industry base</t>
+          <t>General base</t>
         </is>
       </c>
       <c r="G56" s="39" t="inlineStr">
         <is>
-          <t>Prime Super Pty Ltd</t>
+          <t>Diversa Trustees Limited</t>
         </is>
       </c>
       <c r="H56" s="39" t="inlineStr">
         <is>
-          <t>Other ownership type</t>
+          <t>Financial services corporation ownership</t>
         </is>
       </c>
       <c r="I56" s="39" t="inlineStr">
         <is>
-          <t>Not for profit status</t>
+          <t>For profit status</t>
         </is>
       </c>
       <c r="J56" s="39" t="inlineStr">
@@ -15551,39 +15579,39 @@
         </is>
       </c>
       <c r="K56" s="40" t="n">
-        <v>137730</v>
+        <v>15280</v>
       </c>
       <c r="L56" s="40" t="n">
-        <v>8483829</v>
+        <v>5452754</v>
       </c>
       <c r="M56" s="40" t="inlineStr">
         <is>
-          <t>$15,000 to $24,999</t>
+          <t>$200,000 to $499,999</t>
         </is>
       </c>
       <c r="N56" s="40" t="n">
-        <v>16497</v>
+        <v>273087</v>
       </c>
       <c r="O56" s="40" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="P56" s="40" t="n">
-        <v>104780</v>
+        <v>15200</v>
       </c>
       <c r="Q56" s="40" t="n">
-        <v>32950</v>
+        <v>80</v>
       </c>
       <c r="R56" s="40" t="n">
-        <v>7269959</v>
+        <v>5450124</v>
       </c>
       <c r="S56" s="40" t="n">
-        <v>1213869</v>
+        <v>2630</v>
       </c>
       <c r="T56" s="40" t="n">
-        <v>69.40000000000001</v>
+        <v>358.7</v>
       </c>
       <c r="U56" s="40" t="n">
-        <v>36.8</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="57" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -15592,35 +15620,35 @@
       </c>
       <c r="B57" s="39" t="inlineStr">
         <is>
-          <t>Public Sector Superannuation Accumulation Plan</t>
+          <t>Prime Super</t>
         </is>
       </c>
       <c r="C57" s="39" t="n">
-        <v>65127917725</v>
+        <v>60562335823</v>
       </c>
       <c r="D57" s="39" t="inlineStr">
         <is>
-          <t>non-public offer</t>
+          <t>public offer</t>
         </is>
       </c>
       <c r="E57" s="39" t="inlineStr">
         <is>
-          <t>PUBLIC_SECTOR</t>
+          <t>INDUSTRY</t>
         </is>
       </c>
       <c r="F57" s="39" t="inlineStr">
         <is>
-          <t>Government base</t>
+          <t>Industry base</t>
         </is>
       </c>
       <c r="G57" s="39" t="inlineStr">
         <is>
-          <t>Commonwealth Superannuation Corporation</t>
+          <t>Prime Super Pty Ltd</t>
         </is>
       </c>
       <c r="H57" s="39" t="inlineStr">
         <is>
-          <t>Public sector organisation ownership</t>
+          <t>Other ownership type</t>
         </is>
       </c>
       <c r="I57" s="39" t="inlineStr">
@@ -15630,43 +15658,43 @@
       </c>
       <c r="J57" s="39" t="inlineStr">
         <is>
-          <t>Equal representation required by legislation</t>
+          <t>Non equal representation</t>
         </is>
       </c>
       <c r="K57" s="40" t="n">
-        <v>175170</v>
+        <v>137730</v>
       </c>
       <c r="L57" s="40" t="n">
-        <v>32407871</v>
+        <v>8483829</v>
       </c>
       <c r="M57" s="40" t="inlineStr">
         <is>
-          <t>$100,000 to $199,999</t>
+          <t>$15,000 to $24,999</t>
         </is>
       </c>
       <c r="N57" s="40" t="n">
-        <v>125376</v>
+        <v>16497</v>
       </c>
       <c r="O57" s="40" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="P57" s="40" t="n">
-        <v>150310</v>
+        <v>104780</v>
       </c>
       <c r="Q57" s="40" t="n">
-        <v>24860</v>
+        <v>32950</v>
       </c>
       <c r="R57" s="40" t="n">
-        <v>29297900</v>
+        <v>7269959</v>
       </c>
       <c r="S57" s="40" t="n">
-        <v>3109972</v>
+        <v>1213869</v>
       </c>
       <c r="T57" s="40" t="n">
-        <v>194.9</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="U57" s="40" t="n">
-        <v>125.1</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="58" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -15675,11 +15703,11 @@
       </c>
       <c r="B58" s="39" t="inlineStr">
         <is>
-          <t>Public Sector Superannuation Scheme</t>
+          <t>Public Sector Superannuation Accumulation Plan</t>
         </is>
       </c>
       <c r="C58" s="39" t="n">
-        <v>74172177893</v>
+        <v>65127917725</v>
       </c>
       <c r="D58" s="39" t="inlineStr">
         <is>
@@ -15717,39 +15745,39 @@
         </is>
       </c>
       <c r="K58" s="40" t="n">
-        <v>206150</v>
+        <v>175170</v>
       </c>
       <c r="L58" s="40" t="n">
-        <v>119996143</v>
+        <v>32407871</v>
       </c>
       <c r="M58" s="40" t="inlineStr">
         <is>
-          <t>$500,000 to $999,999</t>
+          <t>$100,000 to $199,999</t>
         </is>
       </c>
       <c r="N58" s="40" t="n">
-        <v>591585</v>
+        <v>125376</v>
       </c>
       <c r="O58" s="40" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="P58" s="40" t="n">
-        <v>206150</v>
+        <v>150310</v>
       </c>
       <c r="Q58" s="40" t="n">
-        <v>0</v>
+        <v>24860</v>
       </c>
       <c r="R58" s="40" t="n">
-        <v>119996143</v>
+        <v>29297900</v>
       </c>
       <c r="S58" s="40" t="n">
-        <v>0</v>
+        <v>3109972</v>
       </c>
       <c r="T58" s="40" t="n">
-        <v>582.1</v>
+        <v>194.9</v>
       </c>
       <c r="U58" s="40" t="n">
-        <v>0</v>
+        <v>125.1</v>
       </c>
     </row>
     <row r="59" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -15758,35 +15786,35 @@
       </c>
       <c r="B59" s="39" t="inlineStr">
         <is>
-          <t>Rei Super</t>
+          <t>Public Sector Superannuation Scheme</t>
         </is>
       </c>
       <c r="C59" s="39" t="n">
-        <v>76641658449</v>
+        <v>74172177893</v>
       </c>
       <c r="D59" s="39" t="inlineStr">
         <is>
-          <t>public offer</t>
+          <t>non-public offer</t>
         </is>
       </c>
       <c r="E59" s="39" t="inlineStr">
         <is>
-          <t>INDUSTRY</t>
+          <t>PUBLIC_SECTOR</t>
         </is>
       </c>
       <c r="F59" s="39" t="inlineStr">
         <is>
-          <t>Industry base</t>
+          <t>Government base</t>
         </is>
       </c>
       <c r="G59" s="39" t="inlineStr">
         <is>
-          <t>Rei Superannuation Fund Pty Limited</t>
+          <t>Commonwealth Superannuation Corporation</t>
         </is>
       </c>
       <c r="H59" s="39" t="inlineStr">
         <is>
-          <t>Nominating organisation ownership</t>
+          <t>Public sector organisation ownership</t>
         </is>
       </c>
       <c r="I59" s="39" t="inlineStr">
@@ -15796,43 +15824,43 @@
       </c>
       <c r="J59" s="39" t="inlineStr">
         <is>
-          <t>Non equal representation</t>
+          <t>Equal representation required by legislation</t>
         </is>
       </c>
       <c r="K59" s="40" t="n">
-        <v>24520</v>
+        <v>206150</v>
       </c>
       <c r="L59" s="40" t="n">
-        <v>2587976</v>
+        <v>119996143</v>
       </c>
       <c r="M59" s="40" t="inlineStr">
         <is>
-          <t>$40,000 to $59,999</t>
+          <t>$500,000 to $999,999</t>
         </is>
       </c>
       <c r="N59" s="40" t="n">
-        <v>52540</v>
+        <v>591585</v>
       </c>
       <c r="O59" s="40" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="P59" s="40" t="n">
-        <v>22210</v>
+        <v>206150</v>
       </c>
       <c r="Q59" s="40" t="n">
-        <v>2310</v>
+        <v>0</v>
       </c>
       <c r="R59" s="40" t="n">
-        <v>2513199</v>
+        <v>119996143</v>
       </c>
       <c r="S59" s="40" t="n">
-        <v>74777</v>
+        <v>0</v>
       </c>
       <c r="T59" s="40" t="n">
-        <v>113.2</v>
+        <v>582.1</v>
       </c>
       <c r="U59" s="40" t="n">
-        <v>32.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -15841,11 +15869,11 @@
       </c>
       <c r="B60" s="39" t="inlineStr">
         <is>
-          <t>Retail Employees Superannuation Trust</t>
+          <t>Rei Super</t>
         </is>
       </c>
       <c r="C60" s="39" t="n">
-        <v>62653671394</v>
+        <v>76641658449</v>
       </c>
       <c r="D60" s="39" t="inlineStr">
         <is>
@@ -15864,7 +15892,7 @@
       </c>
       <c r="G60" s="39" t="inlineStr">
         <is>
-          <t>Retail Employees Superannuation Pty. Limited</t>
+          <t>Rei Superannuation Fund Pty Limited</t>
         </is>
       </c>
       <c r="H60" s="39" t="inlineStr">
@@ -15879,43 +15907,43 @@
       </c>
       <c r="J60" s="39" t="inlineStr">
         <is>
-          <t>Equal representation required by governing rules</t>
+          <t>Non equal representation</t>
         </is>
       </c>
       <c r="K60" s="40" t="n">
-        <v>2165690</v>
+        <v>24520</v>
       </c>
       <c r="L60" s="40" t="n">
-        <v>104955081</v>
+        <v>2587976</v>
       </c>
       <c r="M60" s="40" t="inlineStr">
         <is>
-          <t>$15,000 to $24,999</t>
+          <t>$40,000 to $59,999</t>
         </is>
       </c>
       <c r="N60" s="40" t="n">
-        <v>18856</v>
+        <v>52540</v>
       </c>
       <c r="O60" s="40" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="P60" s="40" t="n">
-        <v>1844830</v>
+        <v>22210</v>
       </c>
       <c r="Q60" s="40" t="n">
-        <v>320860</v>
+        <v>2310</v>
       </c>
       <c r="R60" s="40" t="n">
-        <v>93265016</v>
+        <v>2513199</v>
       </c>
       <c r="S60" s="40" t="n">
-        <v>11690064</v>
+        <v>74777</v>
       </c>
       <c r="T60" s="40" t="n">
-        <v>50.6</v>
+        <v>113.2</v>
       </c>
       <c r="U60" s="40" t="n">
-        <v>36.4</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="61" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -15924,11 +15952,11 @@
       </c>
       <c r="B61" s="39" t="inlineStr">
         <is>
-          <t>Retirement Portfolio Service</t>
+          <t>Retail Employees Superannuation Trust</t>
         </is>
       </c>
       <c r="C61" s="39" t="n">
-        <v>61808189263</v>
+        <v>62653671394</v>
       </c>
       <c r="D61" s="39" t="inlineStr">
         <is>
@@ -15937,68 +15965,68 @@
       </c>
       <c r="E61" s="39" t="inlineStr">
         <is>
-          <t>RETAIL</t>
+          <t>INDUSTRY</t>
         </is>
       </c>
       <c r="F61" s="39" t="inlineStr">
         <is>
-          <t>General base</t>
+          <t>Industry base</t>
         </is>
       </c>
       <c r="G61" s="39" t="inlineStr">
         <is>
-          <t>OnePath Custodians Pty Limited</t>
+          <t>Retail Employees Superannuation Pty. Limited</t>
         </is>
       </c>
       <c r="H61" s="39" t="inlineStr">
         <is>
-          <t>Financial services corporation ownership</t>
+          <t>Nominating organisation ownership</t>
         </is>
       </c>
       <c r="I61" s="39" t="inlineStr">
         <is>
-          <t>For profit status</t>
+          <t>Not for profit status</t>
         </is>
       </c>
       <c r="J61" s="39" t="inlineStr">
         <is>
-          <t>Non equal representation</t>
+          <t>Equal representation required by governing rules</t>
         </is>
       </c>
       <c r="K61" s="40" t="n">
-        <v>370290</v>
+        <v>2165690</v>
       </c>
       <c r="L61" s="40" t="n">
-        <v>40111732</v>
+        <v>104955081</v>
       </c>
       <c r="M61" s="40" t="inlineStr">
         <is>
-          <t>$40,000 to $59,999</t>
+          <t>$15,000 to $24,999</t>
         </is>
       </c>
       <c r="N61" s="40" t="n">
-        <v>49590</v>
+        <v>18856</v>
       </c>
       <c r="O61" s="40" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="P61" s="40" t="n">
-        <v>241170</v>
+        <v>1844830</v>
       </c>
       <c r="Q61" s="40" t="n">
-        <v>129120</v>
+        <v>320860</v>
       </c>
       <c r="R61" s="40" t="n">
-        <v>32645172</v>
+        <v>93265016</v>
       </c>
       <c r="S61" s="40" t="n">
-        <v>7466561</v>
+        <v>11690064</v>
       </c>
       <c r="T61" s="40" t="n">
-        <v>135.4</v>
+        <v>50.6</v>
       </c>
       <c r="U61" s="40" t="n">
-        <v>57.8</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="62" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -16007,15 +16035,15 @@
       </c>
       <c r="B62" s="39" t="inlineStr">
         <is>
-          <t>Rexel Australia Superannuation Plan</t>
+          <t>Retirement Portfolio Service</t>
         </is>
       </c>
       <c r="C62" s="39" t="n">
-        <v>73706435443</v>
+        <v>61808189263</v>
       </c>
       <c r="D62" s="39" t="inlineStr">
         <is>
-          <t>non-public offer</t>
+          <t>public offer</t>
         </is>
       </c>
       <c r="E62" s="39" t="inlineStr">
@@ -16030,7 +16058,7 @@
       </c>
       <c r="G62" s="39" t="inlineStr">
         <is>
-          <t>Diversa Trustees Limited</t>
+          <t>OnePath Custodians Pty Limited</t>
         </is>
       </c>
       <c r="H62" s="39" t="inlineStr">
@@ -16049,39 +16077,39 @@
         </is>
       </c>
       <c r="K62" s="40" t="n">
-        <v>20</v>
+        <v>370290</v>
       </c>
       <c r="L62" s="40" t="n">
-        <v>11190</v>
+        <v>40111732</v>
       </c>
       <c r="M62" s="40" t="inlineStr">
         <is>
-          <t>$200,000 to $499,999</t>
+          <t>$40,000 to $59,999</t>
         </is>
       </c>
       <c r="N62" s="40" t="n">
-        <v>464617</v>
+        <v>49590</v>
       </c>
       <c r="O62" s="40" t="n">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="P62" s="40" t="n">
-        <v>20</v>
+        <v>241170</v>
       </c>
       <c r="Q62" s="40" t="n">
-        <v>0</v>
+        <v>129120</v>
       </c>
       <c r="R62" s="40" t="n">
-        <v>11190</v>
+        <v>32645172</v>
       </c>
       <c r="S62" s="40" t="n">
-        <v>0</v>
+        <v>7466561</v>
       </c>
       <c r="T62" s="40" t="n">
-        <v>559.5</v>
+        <v>135.4</v>
       </c>
       <c r="U62" s="40" t="n">
-        <v>0</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="63" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -16090,15 +16118,15 @@
       </c>
       <c r="B63" s="39" t="inlineStr">
         <is>
-          <t>Russell Investments Master Trust</t>
+          <t>Rexel Australia Superannuation Plan</t>
         </is>
       </c>
       <c r="C63" s="39" t="n">
-        <v>89384753567</v>
+        <v>73706435443</v>
       </c>
       <c r="D63" s="39" t="inlineStr">
         <is>
-          <t>public offer</t>
+          <t>non-public offer</t>
         </is>
       </c>
       <c r="E63" s="39" t="inlineStr">
@@ -16108,12 +16136,12 @@
       </c>
       <c r="F63" s="39" t="inlineStr">
         <is>
-          <t>Corporate base</t>
+          <t>General base</t>
         </is>
       </c>
       <c r="G63" s="39" t="inlineStr">
         <is>
-          <t>Total Risk Management Pty Limited</t>
+          <t>Diversa Trustees Limited</t>
         </is>
       </c>
       <c r="H63" s="39" t="inlineStr">
@@ -16132,39 +16160,39 @@
         </is>
       </c>
       <c r="K63" s="40" t="n">
-        <v>82770</v>
+        <v>20</v>
       </c>
       <c r="L63" s="40" t="n">
-        <v>12496612</v>
+        <v>11190</v>
       </c>
       <c r="M63" s="40" t="inlineStr">
         <is>
-          <t>$40,000 to $59,999</t>
+          <t>$200,000 to $499,999</t>
         </is>
       </c>
       <c r="N63" s="40" t="n">
-        <v>48639</v>
+        <v>464617</v>
       </c>
       <c r="O63" s="40" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="P63" s="40" t="n">
-        <v>60660</v>
+        <v>20</v>
       </c>
       <c r="Q63" s="40" t="n">
-        <v>22110</v>
+        <v>0</v>
       </c>
       <c r="R63" s="40" t="n">
-        <v>10411677</v>
+        <v>11190</v>
       </c>
       <c r="S63" s="40" t="n">
-        <v>2084935</v>
+        <v>0</v>
       </c>
       <c r="T63" s="40" t="n">
-        <v>171.6</v>
+        <v>559.5</v>
       </c>
       <c r="U63" s="40" t="n">
-        <v>94.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -16173,11 +16201,11 @@
       </c>
       <c r="B64" s="39" t="inlineStr">
         <is>
-          <t>Smart Future Trust</t>
+          <t>Russell Investments Master Trust</t>
         </is>
       </c>
       <c r="C64" s="39" t="n">
-        <v>68964712340</v>
+        <v>89384753567</v>
       </c>
       <c r="D64" s="39" t="inlineStr">
         <is>
@@ -16191,12 +16219,12 @@
       </c>
       <c r="F64" s="39" t="inlineStr">
         <is>
-          <t>General base</t>
+          <t>Corporate base</t>
         </is>
       </c>
       <c r="G64" s="39" t="inlineStr">
         <is>
-          <t>Equity Trustees Superannuation Limited</t>
+          <t>Total Risk Management Pty Limited</t>
         </is>
       </c>
       <c r="H64" s="39" t="inlineStr">
@@ -16215,39 +16243,39 @@
         </is>
       </c>
       <c r="K64" s="40" t="n">
-        <v>316940</v>
+        <v>82770</v>
       </c>
       <c r="L64" s="40" t="n">
-        <v>9719844</v>
+        <v>12496612</v>
       </c>
       <c r="M64" s="40" t="inlineStr">
         <is>
-          <t>&lt;$1,000</t>
+          <t>$40,000 to $59,999</t>
         </is>
       </c>
       <c r="N64" s="40" t="n">
-        <v>489</v>
+        <v>48639</v>
       </c>
       <c r="O64" s="40" t="n">
         <v>45</v>
       </c>
       <c r="P64" s="40" t="n">
-        <v>312700</v>
+        <v>60660</v>
       </c>
       <c r="Q64" s="40" t="n">
-        <v>4240</v>
+        <v>22110</v>
       </c>
       <c r="R64" s="40" t="n">
-        <v>9645227</v>
+        <v>10411677</v>
       </c>
       <c r="S64" s="40" t="n">
-        <v>74617</v>
+        <v>2084935</v>
       </c>
       <c r="T64" s="40" t="n">
-        <v>30.8</v>
+        <v>171.6</v>
       </c>
       <c r="U64" s="40" t="n">
-        <v>17.6</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="65" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -16256,11 +16284,11 @@
       </c>
       <c r="B65" s="39" t="inlineStr">
         <is>
-          <t>Super Retirement Fund</t>
+          <t>Smart Future Trust</t>
         </is>
       </c>
       <c r="C65" s="39" t="n">
-        <v>40328908469</v>
+        <v>68964712340</v>
       </c>
       <c r="D65" s="39" t="inlineStr">
         <is>
@@ -16298,39 +16326,39 @@
         </is>
       </c>
       <c r="K65" s="40" t="n">
-        <v>28120</v>
+        <v>316940</v>
       </c>
       <c r="L65" s="40" t="n">
-        <v>2569273</v>
+        <v>9719844</v>
       </c>
       <c r="M65" s="40" t="inlineStr">
         <is>
-          <t>$40,000 to $59,999</t>
+          <t>&lt;$1,000</t>
         </is>
       </c>
       <c r="N65" s="40" t="n">
-        <v>45824</v>
+        <v>489</v>
       </c>
       <c r="O65" s="40" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="P65" s="40" t="n">
-        <v>3900</v>
+        <v>312700</v>
       </c>
       <c r="Q65" s="40" t="n">
-        <v>24220</v>
+        <v>4240</v>
       </c>
       <c r="R65" s="40" t="n">
-        <v>379042</v>
+        <v>9645227</v>
       </c>
       <c r="S65" s="40" t="n">
-        <v>2190230</v>
+        <v>74617</v>
       </c>
       <c r="T65" s="40" t="n">
-        <v>97.09999999999999</v>
+        <v>30.8</v>
       </c>
       <c r="U65" s="40" t="n">
-        <v>90.40000000000001</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="66" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -16339,11 +16367,11 @@
       </c>
       <c r="B66" s="39" t="inlineStr">
         <is>
-          <t>Super Simplifier</t>
+          <t>Super Retirement Fund</t>
         </is>
       </c>
       <c r="C66" s="39" t="n">
-        <v>36526795205</v>
+        <v>40328908469</v>
       </c>
       <c r="D66" s="39" t="inlineStr">
         <is>
@@ -16381,39 +16409,39 @@
         </is>
       </c>
       <c r="K66" s="40" t="n">
-        <v>6760</v>
+        <v>28120</v>
       </c>
       <c r="L66" s="40" t="n">
-        <v>1712773</v>
+        <v>2569273</v>
       </c>
       <c r="M66" s="40" t="inlineStr">
         <is>
-          <t>$100,000 to $199,999</t>
+          <t>$40,000 to $59,999</t>
         </is>
       </c>
       <c r="N66" s="40" t="n">
-        <v>160150</v>
+        <v>45824</v>
       </c>
       <c r="O66" s="40" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="P66" s="40" t="n">
-        <v>6140</v>
+        <v>3900</v>
       </c>
       <c r="Q66" s="40" t="n">
-        <v>610</v>
+        <v>24220</v>
       </c>
       <c r="R66" s="40" t="n">
-        <v>1580663</v>
+        <v>379042</v>
       </c>
       <c r="S66" s="40" t="n">
-        <v>132110</v>
+        <v>2190230</v>
       </c>
       <c r="T66" s="40" t="n">
-        <v>257.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="U66" s="40" t="n">
-        <v>215.5</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="67" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -16422,11 +16450,11 @@
       </c>
       <c r="B67" s="39" t="inlineStr">
         <is>
-          <t>Team Superannuation Fund</t>
+          <t>Super Simplifier</t>
         </is>
       </c>
       <c r="C67" s="39" t="n">
-        <v>16457520308</v>
+        <v>36526795205</v>
       </c>
       <c r="D67" s="39" t="inlineStr">
         <is>
@@ -16435,68 +16463,68 @@
       </c>
       <c r="E67" s="39" t="inlineStr">
         <is>
-          <t>INDUSTRY</t>
+          <t>RETAIL</t>
         </is>
       </c>
       <c r="F67" s="39" t="inlineStr">
         <is>
-          <t>Industry base</t>
+          <t>General base</t>
         </is>
       </c>
       <c r="G67" s="39" t="inlineStr">
         <is>
-          <t>Team Super Pty Ltd</t>
+          <t>Equity Trustees Superannuation Limited</t>
         </is>
       </c>
       <c r="H67" s="39" t="inlineStr">
         <is>
-          <t>Nominating organisation ownership</t>
+          <t>Financial services corporation ownership</t>
         </is>
       </c>
       <c r="I67" s="39" t="inlineStr">
         <is>
-          <t>Not for profit status</t>
+          <t>For profit status</t>
         </is>
       </c>
       <c r="J67" s="39" t="inlineStr">
         <is>
-          <t>Equal representation required by governing rules</t>
+          <t>Non equal representation</t>
         </is>
       </c>
       <c r="K67" s="40" t="n">
-        <v>149830</v>
+        <v>6760</v>
       </c>
       <c r="L67" s="40" t="n">
-        <v>22760687</v>
+        <v>1712773</v>
       </c>
       <c r="M67" s="40" t="inlineStr">
         <is>
-          <t>$60,000 to $99,999</t>
+          <t>$100,000 to $199,999</t>
         </is>
       </c>
       <c r="N67" s="40" t="n">
-        <v>66821</v>
+        <v>160150</v>
       </c>
       <c r="O67" s="40" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="P67" s="40" t="n">
-        <v>141710</v>
+        <v>6140</v>
       </c>
       <c r="Q67" s="40" t="n">
-        <v>8120</v>
+        <v>610</v>
       </c>
       <c r="R67" s="40" t="n">
-        <v>21531532</v>
+        <v>1580663</v>
       </c>
       <c r="S67" s="40" t="n">
-        <v>1229154</v>
+        <v>132110</v>
       </c>
       <c r="T67" s="40" t="n">
-        <v>151.9</v>
+        <v>257.3</v>
       </c>
       <c r="U67" s="40" t="n">
-        <v>151.5</v>
+        <v>215.5</v>
       </c>
     </row>
     <row r="68" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -16505,11 +16533,11 @@
       </c>
       <c r="B68" s="39" t="inlineStr">
         <is>
-          <t>Telstra Superannuation Scheme</t>
+          <t>Team Superannuation Fund</t>
         </is>
       </c>
       <c r="C68" s="39" t="n">
-        <v>85502108833</v>
+        <v>16457520308</v>
       </c>
       <c r="D68" s="39" t="inlineStr">
         <is>
@@ -16518,22 +16546,22 @@
       </c>
       <c r="E68" s="39" t="inlineStr">
         <is>
-          <t>CORPORATE</t>
+          <t>INDUSTRY</t>
         </is>
       </c>
       <c r="F68" s="39" t="inlineStr">
         <is>
-          <t>General base</t>
+          <t>Industry base</t>
         </is>
       </c>
       <c r="G68" s="39" t="inlineStr">
         <is>
-          <t>Telstra Super Pty Ltd</t>
+          <t>Team Super Pty Ltd</t>
         </is>
       </c>
       <c r="H68" s="39" t="inlineStr">
         <is>
-          <t>Employer sponsor (non-public sector) ownership</t>
+          <t>Nominating organisation ownership</t>
         </is>
       </c>
       <c r="I68" s="39" t="inlineStr">
@@ -16547,39 +16575,39 @@
         </is>
       </c>
       <c r="K68" s="40" t="n">
-        <v>97210</v>
+        <v>149830</v>
       </c>
       <c r="L68" s="40" t="n">
-        <v>28137324</v>
+        <v>22760687</v>
       </c>
       <c r="M68" s="40" t="inlineStr">
         <is>
-          <t>$100,000 to $199,999</t>
+          <t>$60,000 to $99,999</t>
         </is>
       </c>
       <c r="N68" s="40" t="n">
-        <v>156931</v>
+        <v>66821</v>
       </c>
       <c r="O68" s="40" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="P68" s="40" t="n">
-        <v>72940</v>
+        <v>141710</v>
       </c>
       <c r="Q68" s="40" t="n">
-        <v>24260</v>
+        <v>8120</v>
       </c>
       <c r="R68" s="40" t="n">
-        <v>23244619</v>
+        <v>21531532</v>
       </c>
       <c r="S68" s="40" t="n">
-        <v>4892704</v>
+        <v>1229154</v>
       </c>
       <c r="T68" s="40" t="n">
-        <v>318.7</v>
+        <v>151.9</v>
       </c>
       <c r="U68" s="40" t="n">
-        <v>201.7</v>
+        <v>151.5</v>
       </c>
     </row>
     <row r="69" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -16588,11 +16616,11 @@
       </c>
       <c r="B69" s="39" t="inlineStr">
         <is>
-          <t>The Bendigo Superannuation Plan</t>
+          <t>Telstra Superannuation Scheme</t>
         </is>
       </c>
       <c r="C69" s="39" t="n">
-        <v>57526653420</v>
+        <v>85502108833</v>
       </c>
       <c r="D69" s="39" t="inlineStr">
         <is>
@@ -16601,7 +16629,7 @@
       </c>
       <c r="E69" s="39" t="inlineStr">
         <is>
-          <t>RETAIL</t>
+          <t>CORPORATE</t>
         </is>
       </c>
       <c r="F69" s="39" t="inlineStr">
@@ -16611,58 +16639,58 @@
       </c>
       <c r="G69" s="39" t="inlineStr">
         <is>
-          <t>Bendigo Superannuation Pty Ltd</t>
+          <t>Telstra Super Pty Ltd</t>
         </is>
       </c>
       <c r="H69" s="39" t="inlineStr">
         <is>
-          <t>Financial services corporation ownership</t>
+          <t>Employer sponsor (non-public sector) ownership</t>
         </is>
       </c>
       <c r="I69" s="39" t="inlineStr">
         <is>
-          <t>For profit status</t>
+          <t>Not for profit status</t>
         </is>
       </c>
       <c r="J69" s="39" t="inlineStr">
         <is>
-          <t>Non equal representation</t>
+          <t>Equal representation required by governing rules</t>
         </is>
       </c>
       <c r="K69" s="40" t="n">
-        <v>15350</v>
+        <v>97210</v>
       </c>
       <c r="L69" s="40" t="n">
-        <v>1530815</v>
+        <v>28137324</v>
       </c>
       <c r="M69" s="40" t="inlineStr">
         <is>
-          <t>$40,000 to $59,999</t>
+          <t>$100,000 to $199,999</t>
         </is>
       </c>
       <c r="N69" s="40" t="n">
-        <v>49577</v>
+        <v>156931</v>
       </c>
       <c r="O69" s="40" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="P69" s="40" t="n">
-        <v>11950</v>
+        <v>72940</v>
       </c>
       <c r="Q69" s="40" t="n">
-        <v>3400</v>
+        <v>24260</v>
       </c>
       <c r="R69" s="40" t="n">
-        <v>1267094</v>
+        <v>23244619</v>
       </c>
       <c r="S69" s="40" t="n">
-        <v>263721</v>
+        <v>4892704</v>
       </c>
       <c r="T69" s="40" t="n">
-        <v>106</v>
+        <v>318.7</v>
       </c>
       <c r="U69" s="40" t="n">
-        <v>77.59999999999999</v>
+        <v>201.7</v>
       </c>
     </row>
     <row r="70" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -16671,15 +16699,15 @@
       </c>
       <c r="B70" s="39" t="inlineStr">
         <is>
-          <t>The University of New England Professorial Superannuation Fund</t>
+          <t>The Bendigo Superannuation Plan</t>
         </is>
       </c>
       <c r="C70" s="39" t="n">
-        <v>42142142507</v>
+        <v>57526653420</v>
       </c>
       <c r="D70" s="39" t="inlineStr">
         <is>
-          <t>non-public offer</t>
+          <t>public offer</t>
         </is>
       </c>
       <c r="E70" s="39" t="inlineStr">
@@ -16694,7 +16722,7 @@
       </c>
       <c r="G70" s="39" t="inlineStr">
         <is>
-          <t>Diversa Trustees Limited</t>
+          <t>Bendigo Superannuation Pty Ltd</t>
         </is>
       </c>
       <c r="H70" s="39" t="inlineStr">
@@ -16712,60 +16740,40 @@
           <t>Non equal representation</t>
         </is>
       </c>
-      <c r="K70" s="40" t="inlineStr">
-        <is>
-          <t>&lt;20</t>
-        </is>
-      </c>
-      <c r="L70" s="40" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
+      <c r="K70" s="40" t="n">
+        <v>15350</v>
+      </c>
+      <c r="L70" s="40" t="n">
+        <v>1530815</v>
       </c>
       <c r="M70" s="40" t="inlineStr">
         <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="N70" s="40" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="O70" s="40" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="P70" s="40" t="inlineStr">
-        <is>
-          <t>&lt;20</t>
-        </is>
-      </c>
-      <c r="Q70" s="40" t="inlineStr">
-        <is>
-          <t>&lt;20</t>
-        </is>
-      </c>
-      <c r="R70" s="40" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="S70" s="40" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="T70" s="40" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="U70" s="40" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
+          <t>$40,000 to $59,999</t>
+        </is>
+      </c>
+      <c r="N70" s="40" t="n">
+        <v>49577</v>
+      </c>
+      <c r="O70" s="40" t="n">
+        <v>50</v>
+      </c>
+      <c r="P70" s="40" t="n">
+        <v>11950</v>
+      </c>
+      <c r="Q70" s="40" t="n">
+        <v>3400</v>
+      </c>
+      <c r="R70" s="40" t="n">
+        <v>1267094</v>
+      </c>
+      <c r="S70" s="40" t="n">
+        <v>263721</v>
+      </c>
+      <c r="T70" s="40" t="n">
+        <v>106</v>
+      </c>
+      <c r="U70" s="40" t="n">
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="71" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -16774,11 +16782,11 @@
       </c>
       <c r="B71" s="39" t="inlineStr">
         <is>
-          <t>The University of New South Wales Professorial Superannuation Fund</t>
+          <t>The University of New England Professorial Superannuation Fund</t>
         </is>
       </c>
       <c r="C71" s="39" t="n">
-        <v>12007600799</v>
+        <v>42142142507</v>
       </c>
       <c r="D71" s="39" t="inlineStr">
         <is>
@@ -16815,40 +16823,60 @@
           <t>Non equal representation</t>
         </is>
       </c>
-      <c r="K71" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="L71" s="40" t="n">
-        <v>22766</v>
+      <c r="K71" s="40" t="inlineStr">
+        <is>
+          <t>&lt;20</t>
+        </is>
+      </c>
+      <c r="L71" s="40" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
       </c>
       <c r="M71" s="40" t="inlineStr">
         <is>
-          <t>$200,000 to $499,999</t>
-        </is>
-      </c>
-      <c r="N71" s="40" t="n">
-        <v>363954</v>
-      </c>
-      <c r="O71" s="40" t="n">
-        <v>86</v>
-      </c>
-      <c r="P71" s="40" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q71" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" s="40" t="n">
-        <v>22766</v>
-      </c>
-      <c r="S71" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T71" s="40" t="n">
-        <v>385.9</v>
-      </c>
-      <c r="U71" s="40" t="n">
-        <v>0</v>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="N71" s="40" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="O71" s="40" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="P71" s="40" t="inlineStr">
+        <is>
+          <t>&lt;20</t>
+        </is>
+      </c>
+      <c r="Q71" s="40" t="inlineStr">
+        <is>
+          <t>&lt;20</t>
+        </is>
+      </c>
+      <c r="R71" s="40" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="S71" s="40" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="T71" s="40" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="U71" s="40" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
       </c>
     </row>
     <row r="72" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -16857,15 +16885,15 @@
       </c>
       <c r="B72" s="39" t="inlineStr">
         <is>
-          <t>The University of Sydney Professorial Superannuation System</t>
+          <t>The University of New South Wales Professorial Superannuation Fund</t>
         </is>
       </c>
       <c r="C72" s="39" t="n">
-        <v>70093025653</v>
+        <v>12007600799</v>
       </c>
       <c r="D72" s="39" t="inlineStr">
         <is>
-          <t>public offer</t>
+          <t>non-public offer</t>
         </is>
       </c>
       <c r="E72" s="39" t="inlineStr">
@@ -16899,10 +16927,10 @@
         </is>
       </c>
       <c r="K72" s="40" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="L72" s="40" t="n">
-        <v>14006</v>
+        <v>22766</v>
       </c>
       <c r="M72" s="40" t="inlineStr">
         <is>
@@ -16910,25 +16938,25 @@
         </is>
       </c>
       <c r="N72" s="40" t="n">
-        <v>384257</v>
+        <v>363954</v>
       </c>
       <c r="O72" s="40" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P72" s="40" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="Q72" s="40" t="n">
         <v>0</v>
       </c>
       <c r="R72" s="40" t="n">
-        <v>14006</v>
+        <v>22766</v>
       </c>
       <c r="S72" s="40" t="n">
         <v>0</v>
       </c>
       <c r="T72" s="40" t="n">
-        <v>411.9</v>
+        <v>385.9</v>
       </c>
       <c r="U72" s="40" t="n">
         <v>0</v>
@@ -16940,11 +16968,11 @@
       </c>
       <c r="B73" s="39" t="inlineStr">
         <is>
-          <t>The University of Wollongong Professorial Superannuation Scheme</t>
+          <t>The University of Sydney Professorial Superannuation System</t>
         </is>
       </c>
       <c r="C73" s="39" t="n">
-        <v>68672265781</v>
+        <v>70093025653</v>
       </c>
       <c r="D73" s="39" t="inlineStr">
         <is>
@@ -16981,60 +17009,40 @@
           <t>Non equal representation</t>
         </is>
       </c>
-      <c r="K73" s="40" t="inlineStr">
-        <is>
-          <t>&lt;20</t>
-        </is>
-      </c>
-      <c r="L73" s="40" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
+      <c r="K73" s="40" t="n">
+        <v>30</v>
+      </c>
+      <c r="L73" s="40" t="n">
+        <v>14006</v>
       </c>
       <c r="M73" s="40" t="inlineStr">
         <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="N73" s="40" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="O73" s="40" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="P73" s="40" t="inlineStr">
-        <is>
-          <t>&lt;20</t>
-        </is>
-      </c>
-      <c r="Q73" s="40" t="inlineStr">
-        <is>
-          <t>&lt;20</t>
-        </is>
-      </c>
-      <c r="R73" s="40" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="S73" s="40" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="T73" s="40" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="U73" s="40" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
+          <t>$200,000 to $499,999</t>
+        </is>
+      </c>
+      <c r="N73" s="40" t="n">
+        <v>384257</v>
+      </c>
+      <c r="O73" s="40" t="n">
+        <v>87</v>
+      </c>
+      <c r="P73" s="40" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q73" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" s="40" t="n">
+        <v>14006</v>
+      </c>
+      <c r="S73" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" s="40" t="n">
+        <v>411.9</v>
+      </c>
+      <c r="U73" s="40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -17043,11 +17051,11 @@
       </c>
       <c r="B74" s="39" t="inlineStr">
         <is>
-          <t>Tidswell Master Superannuation Plan</t>
+          <t>The University of Wollongong Professorial Superannuation Scheme</t>
         </is>
       </c>
       <c r="C74" s="39" t="n">
-        <v>34300938877</v>
+        <v>68672265781</v>
       </c>
       <c r="D74" s="39" t="inlineStr">
         <is>
@@ -17084,40 +17092,60 @@
           <t>Non equal representation</t>
         </is>
       </c>
-      <c r="K74" s="40" t="n">
-        <v>2560</v>
-      </c>
-      <c r="L74" s="40" t="n">
-        <v>690568</v>
+      <c r="K74" s="40" t="inlineStr">
+        <is>
+          <t>&lt;20</t>
+        </is>
+      </c>
+      <c r="L74" s="40" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
       </c>
       <c r="M74" s="40" t="inlineStr">
         <is>
-          <t>$200,000 to $499,999</t>
-        </is>
-      </c>
-      <c r="N74" s="40" t="n">
-        <v>222726</v>
-      </c>
-      <c r="O74" s="40" t="n">
-        <v>61</v>
-      </c>
-      <c r="P74" s="40" t="n">
-        <v>1200</v>
-      </c>
-      <c r="Q74" s="40" t="n">
-        <v>1360</v>
-      </c>
-      <c r="R74" s="40" t="n">
-        <v>355030</v>
-      </c>
-      <c r="S74" s="40" t="n">
-        <v>335538</v>
-      </c>
-      <c r="T74" s="40" t="n">
-        <v>296.1</v>
-      </c>
-      <c r="U74" s="40" t="n">
-        <v>246.9</v>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="N74" s="40" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="O74" s="40" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="P74" s="40" t="inlineStr">
+        <is>
+          <t>&lt;20</t>
+        </is>
+      </c>
+      <c r="Q74" s="40" t="inlineStr">
+        <is>
+          <t>&lt;20</t>
+        </is>
+      </c>
+      <c r="R74" s="40" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="S74" s="40" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="T74" s="40" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="U74" s="40" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
       </c>
     </row>
     <row r="75" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -17126,11 +17154,11 @@
       </c>
       <c r="B75" s="39" t="inlineStr">
         <is>
-          <t>Unisuper</t>
+          <t>Tidswell Master Superannuation Plan</t>
         </is>
       </c>
       <c r="C75" s="39" t="n">
-        <v>91385943850</v>
+        <v>34300938877</v>
       </c>
       <c r="D75" s="39" t="inlineStr">
         <is>
@@ -17139,68 +17167,68 @@
       </c>
       <c r="E75" s="39" t="inlineStr">
         <is>
-          <t>INDUSTRY</t>
+          <t>RETAIL</t>
         </is>
       </c>
       <c r="F75" s="39" t="inlineStr">
         <is>
-          <t>Industry base</t>
+          <t>General base</t>
         </is>
       </c>
       <c r="G75" s="39" t="inlineStr">
         <is>
-          <t>Unisuper Limited</t>
+          <t>Diversa Trustees Limited</t>
         </is>
       </c>
       <c r="H75" s="39" t="inlineStr">
         <is>
-          <t>Public company ownership</t>
+          <t>Financial services corporation ownership</t>
         </is>
       </c>
       <c r="I75" s="39" t="inlineStr">
         <is>
-          <t>Not for profit status</t>
+          <t>For profit status</t>
         </is>
       </c>
       <c r="J75" s="39" t="inlineStr">
         <is>
-          <t>Equal representation required by legislation</t>
+          <t>Non equal representation</t>
         </is>
       </c>
       <c r="K75" s="40" t="n">
-        <v>717320</v>
+        <v>2560</v>
       </c>
       <c r="L75" s="40" t="n">
-        <v>152455352</v>
+        <v>690568</v>
       </c>
       <c r="M75" s="40" t="inlineStr">
         <is>
-          <t>$60,000 to $99,999</t>
+          <t>$200,000 to $499,999</t>
         </is>
       </c>
       <c r="N75" s="40" t="n">
-        <v>77163</v>
+        <v>222726</v>
       </c>
       <c r="O75" s="40" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="P75" s="40" t="n">
-        <v>613490</v>
+        <v>1200</v>
       </c>
       <c r="Q75" s="40" t="n">
-        <v>103820</v>
+        <v>1360</v>
       </c>
       <c r="R75" s="40" t="n">
-        <v>137190698</v>
+        <v>355030</v>
       </c>
       <c r="S75" s="40" t="n">
-        <v>15264653</v>
+        <v>335538</v>
       </c>
       <c r="T75" s="40" t="n">
-        <v>223.6</v>
+        <v>296.1</v>
       </c>
       <c r="U75" s="40" t="n">
-        <v>147</v>
+        <v>246.9</v>
       </c>
     </row>
     <row r="76" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -17209,11 +17237,11 @@
       </c>
       <c r="B76" s="39" t="inlineStr">
         <is>
-          <t>Vanguard Super</t>
+          <t>Unisuper</t>
         </is>
       </c>
       <c r="C76" s="39" t="n">
-        <v>27923449966</v>
+        <v>91385943850</v>
       </c>
       <c r="D76" s="39" t="inlineStr">
         <is>
@@ -17222,68 +17250,68 @@
       </c>
       <c r="E76" s="39" t="inlineStr">
         <is>
-          <t>RETAIL</t>
+          <t>INDUSTRY</t>
         </is>
       </c>
       <c r="F76" s="39" t="inlineStr">
         <is>
-          <t>General base</t>
+          <t>Industry base</t>
         </is>
       </c>
       <c r="G76" s="39" t="inlineStr">
         <is>
-          <t>Vanguard Super Pty Ltd</t>
+          <t>Unisuper Limited</t>
         </is>
       </c>
       <c r="H76" s="39" t="inlineStr">
         <is>
-          <t>Other ownership type</t>
+          <t>Public company ownership</t>
         </is>
       </c>
       <c r="I76" s="39" t="inlineStr">
         <is>
-          <t>For profit status</t>
+          <t>Not for profit status</t>
         </is>
       </c>
       <c r="J76" s="39" t="inlineStr">
         <is>
-          <t>Non equal representation</t>
+          <t>Equal representation required by legislation</t>
         </is>
       </c>
       <c r="K76" s="40" t="n">
-        <v>53140</v>
+        <v>717320</v>
       </c>
       <c r="L76" s="40" t="n">
-        <v>4619176</v>
+        <v>152455352</v>
       </c>
       <c r="M76" s="40" t="inlineStr">
         <is>
-          <t>$15,000 to $24,999</t>
+          <t>$60,000 to $99,999</t>
         </is>
       </c>
       <c r="N76" s="40" t="n">
-        <v>18574</v>
+        <v>77163</v>
       </c>
       <c r="O76" s="40" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="P76" s="40" t="n">
-        <v>51810</v>
+        <v>613490</v>
       </c>
       <c r="Q76" s="40" t="n">
-        <v>1320</v>
+        <v>103820</v>
       </c>
       <c r="R76" s="40" t="n">
-        <v>4413552</v>
+        <v>137190698</v>
       </c>
       <c r="S76" s="40" t="n">
-        <v>205624</v>
+        <v>15264653</v>
       </c>
       <c r="T76" s="40" t="n">
-        <v>85.2</v>
+        <v>223.6</v>
       </c>
       <c r="U76" s="40" t="n">
-        <v>155.3</v>
+        <v>147</v>
       </c>
     </row>
     <row r="77" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -17292,11 +17320,11 @@
       </c>
       <c r="B77" s="39" t="inlineStr">
         <is>
-          <t>Wealth Personal Superannuation and Pension Fund</t>
+          <t>Vanguard Super</t>
         </is>
       </c>
       <c r="C77" s="39" t="n">
-        <v>92381911598</v>
+        <v>27923449966</v>
       </c>
       <c r="D77" s="39" t="inlineStr">
         <is>
@@ -17315,12 +17343,12 @@
       </c>
       <c r="G77" s="39" t="inlineStr">
         <is>
-          <t>N. M. Superannuation Proprietary Limited</t>
+          <t>Vanguard Super Pty Ltd</t>
         </is>
       </c>
       <c r="H77" s="39" t="inlineStr">
         <is>
-          <t>Financial services corporation ownership</t>
+          <t>Other ownership type</t>
         </is>
       </c>
       <c r="I77" s="39" t="inlineStr">
@@ -17334,39 +17362,39 @@
         </is>
       </c>
       <c r="K77" s="40" t="n">
-        <v>257710</v>
+        <v>53140</v>
       </c>
       <c r="L77" s="40" t="n">
-        <v>71751364</v>
+        <v>4619176</v>
       </c>
       <c r="M77" s="40" t="inlineStr">
         <is>
-          <t>$100,000 to $199,999</t>
+          <t>$15,000 to $24,999</t>
         </is>
       </c>
       <c r="N77" s="40" t="n">
-        <v>187768</v>
+        <v>18574</v>
       </c>
       <c r="O77" s="40" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="P77" s="40" t="n">
-        <v>220820</v>
+        <v>51810</v>
       </c>
       <c r="Q77" s="40" t="n">
-        <v>36890</v>
+        <v>1320</v>
       </c>
       <c r="R77" s="40" t="n">
-        <v>65629877</v>
+        <v>4413552</v>
       </c>
       <c r="S77" s="40" t="n">
-        <v>6121487</v>
+        <v>205624</v>
       </c>
       <c r="T77" s="40" t="n">
-        <v>297.2</v>
+        <v>85.2</v>
       </c>
       <c r="U77" s="40" t="n">
-        <v>166</v>
+        <v>155.3</v>
       </c>
     </row>
     <row r="78" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -17375,11 +17403,11 @@
       </c>
       <c r="B78" s="39" t="inlineStr">
         <is>
-          <t>Wrap Super</t>
+          <t>Wealth Personal Superannuation and Pension Fund</t>
         </is>
       </c>
       <c r="C78" s="39" t="n">
-        <v>18906079389</v>
+        <v>92381911598</v>
       </c>
       <c r="D78" s="39" t="inlineStr">
         <is>
@@ -17398,7 +17426,7 @@
       </c>
       <c r="G78" s="39" t="inlineStr">
         <is>
-          <t>Equity Trustees Superannuation Limited</t>
+          <t>N. M. Superannuation Proprietary Limited</t>
         </is>
       </c>
       <c r="H78" s="39" t="inlineStr">
@@ -17417,39 +17445,39 @@
         </is>
       </c>
       <c r="K78" s="40" t="n">
-        <v>2020</v>
+        <v>257710</v>
       </c>
       <c r="L78" s="40" t="n">
-        <v>744027</v>
+        <v>71751364</v>
       </c>
       <c r="M78" s="40" t="inlineStr">
         <is>
-          <t>$200,000 to $499,999</t>
+          <t>$100,000 to $199,999</t>
         </is>
       </c>
       <c r="N78" s="40" t="n">
-        <v>299941</v>
+        <v>187768</v>
       </c>
       <c r="O78" s="40" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P78" s="40" t="n">
-        <v>1920</v>
+        <v>220820</v>
       </c>
       <c r="Q78" s="40" t="n">
-        <v>100</v>
+        <v>36890</v>
       </c>
       <c r="R78" s="40" t="n">
-        <v>701496</v>
+        <v>65629877</v>
       </c>
       <c r="S78" s="40" t="n">
-        <v>42532</v>
+        <v>6121487</v>
       </c>
       <c r="T78" s="40" t="n">
-        <v>365</v>
+        <v>297.2</v>
       </c>
       <c r="U78" s="40" t="n">
-        <v>438.5</v>
+        <v>166</v>
       </c>
     </row>
     <row r="79" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -17458,11 +17486,11 @@
       </c>
       <c r="B79" s="39" t="inlineStr">
         <is>
-          <t>equipsuper</t>
+          <t>Wrap Super</t>
         </is>
       </c>
       <c r="C79" s="39" t="n">
-        <v>33813823017</v>
+        <v>18906079389</v>
       </c>
       <c r="D79" s="39" t="inlineStr">
         <is>
@@ -17471,7 +17499,7 @@
       </c>
       <c r="E79" s="39" t="inlineStr">
         <is>
-          <t>INDUSTRY</t>
+          <t>RETAIL</t>
         </is>
       </c>
       <c r="F79" s="39" t="inlineStr">
@@ -17481,17 +17509,17 @@
       </c>
       <c r="G79" s="39" t="inlineStr">
         <is>
-          <t>Togethr Trustees Pty Ltd</t>
+          <t>Equity Trustees Superannuation Limited</t>
         </is>
       </c>
       <c r="H79" s="39" t="inlineStr">
         <is>
-          <t>Other ownership type</t>
+          <t>Financial services corporation ownership</t>
         </is>
       </c>
       <c r="I79" s="39" t="inlineStr">
         <is>
-          <t>Not for profit status</t>
+          <t>For profit status</t>
         </is>
       </c>
       <c r="J79" s="39" t="inlineStr">
@@ -17500,39 +17528,39 @@
         </is>
       </c>
       <c r="K79" s="40" t="n">
-        <v>141660</v>
+        <v>2020</v>
       </c>
       <c r="L79" s="40" t="n">
-        <v>37187430</v>
+        <v>744027</v>
       </c>
       <c r="M79" s="40" t="inlineStr">
         <is>
-          <t>$100,000 to $199,999</t>
+          <t>$200,000 to $499,999</t>
         </is>
       </c>
       <c r="N79" s="40" t="n">
-        <v>136812</v>
+        <v>299941</v>
       </c>
       <c r="O79" s="40" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="P79" s="40" t="n">
-        <v>114820</v>
+        <v>1920</v>
       </c>
       <c r="Q79" s="40" t="n">
-        <v>26850</v>
+        <v>100</v>
       </c>
       <c r="R79" s="40" t="n">
-        <v>32824499</v>
+        <v>701496</v>
       </c>
       <c r="S79" s="40" t="n">
-        <v>4362931</v>
+        <v>42532</v>
       </c>
       <c r="T79" s="40" t="n">
-        <v>285.9</v>
+        <v>365</v>
       </c>
       <c r="U79" s="40" t="n">
-        <v>162.5</v>
+        <v>438.5</v>
       </c>
     </row>
     <row r="80" ht="13.5" customFormat="1" customHeight="1" s="39">
@@ -17541,80 +17569,163 @@
       </c>
       <c r="B80" s="39" t="inlineStr">
         <is>
+          <t>equipsuper</t>
+        </is>
+      </c>
+      <c r="C80" s="39" t="n">
+        <v>33813823017</v>
+      </c>
+      <c r="D80" s="39" t="inlineStr">
+        <is>
+          <t>public offer</t>
+        </is>
+      </c>
+      <c r="E80" s="39" t="inlineStr">
+        <is>
+          <t>INDUSTRY</t>
+        </is>
+      </c>
+      <c r="F80" s="39" t="inlineStr">
+        <is>
+          <t>General base</t>
+        </is>
+      </c>
+      <c r="G80" s="39" t="inlineStr">
+        <is>
+          <t>Togethr Trustees Pty Ltd</t>
+        </is>
+      </c>
+      <c r="H80" s="39" t="inlineStr">
+        <is>
+          <t>Other ownership type</t>
+        </is>
+      </c>
+      <c r="I80" s="39" t="inlineStr">
+        <is>
+          <t>Not for profit status</t>
+        </is>
+      </c>
+      <c r="J80" s="39" t="inlineStr">
+        <is>
+          <t>Non equal representation</t>
+        </is>
+      </c>
+      <c r="K80" s="40" t="n">
+        <v>141660</v>
+      </c>
+      <c r="L80" s="40" t="n">
+        <v>37187430</v>
+      </c>
+      <c r="M80" s="40" t="inlineStr">
+        <is>
+          <t>$100,000 to $199,999</t>
+        </is>
+      </c>
+      <c r="N80" s="40" t="n">
+        <v>136812</v>
+      </c>
+      <c r="O80" s="40" t="n">
+        <v>51</v>
+      </c>
+      <c r="P80" s="40" t="n">
+        <v>114820</v>
+      </c>
+      <c r="Q80" s="40" t="n">
+        <v>26850</v>
+      </c>
+      <c r="R80" s="40" t="n">
+        <v>32824499</v>
+      </c>
+      <c r="S80" s="40" t="n">
+        <v>4362931</v>
+      </c>
+      <c r="T80" s="40" t="n">
+        <v>285.9</v>
+      </c>
+      <c r="U80" s="40" t="n">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="38" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B81" s="39" t="inlineStr">
+        <is>
           <t>legalsuper</t>
         </is>
       </c>
-      <c r="C80" s="39" t="n">
+      <c r="C81" s="39" t="n">
         <v>60346078879</v>
       </c>
-      <c r="D80" s="39" t="inlineStr">
+      <c r="D81" s="39" t="inlineStr">
         <is>
           <t>public offer</t>
         </is>
       </c>
-      <c r="E80" s="39" t="inlineStr">
+      <c r="E81" s="39" t="inlineStr">
         <is>
           <t>INDUSTRY</t>
         </is>
       </c>
-      <c r="F80" s="39" t="inlineStr">
+      <c r="F81" s="39" t="inlineStr">
         <is>
           <t>Industry base</t>
         </is>
       </c>
-      <c r="G80" s="39" t="inlineStr">
+      <c r="G81" s="39" t="inlineStr">
         <is>
           <t>Legal Super Pty Ltd</t>
         </is>
       </c>
-      <c r="H80" s="39" t="inlineStr">
+      <c r="H81" s="39" t="inlineStr">
         <is>
           <t>Nominating organisation ownership</t>
         </is>
       </c>
-      <c r="I80" s="39" t="inlineStr">
+      <c r="I81" s="39" t="inlineStr">
         <is>
           <t>Not for profit status</t>
         </is>
       </c>
-      <c r="J80" s="39" t="inlineStr">
+      <c r="J81" s="39" t="inlineStr">
         <is>
           <t>Equal representation required by governing rules</t>
         </is>
       </c>
-      <c r="K80" s="40" t="n">
+      <c r="K81" s="40" t="n">
         <v>48590</v>
       </c>
-      <c r="L80" s="40" t="n">
+      <c r="L81" s="40" t="n">
         <v>7238576</v>
       </c>
-      <c r="M80" s="40" t="inlineStr">
+      <c r="M81" s="40" t="inlineStr">
         <is>
           <t>$60,000 to $99,999</t>
         </is>
       </c>
-      <c r="N80" s="40" t="n">
+      <c r="N81" s="40" t="n">
         <v>61641</v>
       </c>
-      <c r="O80" s="40" t="n">
+      <c r="O81" s="40" t="n">
         <v>42</v>
       </c>
-      <c r="P80" s="40" t="n">
+      <c r="P81" s="40" t="n">
         <v>39170</v>
       </c>
-      <c r="Q80" s="40" t="n">
+      <c r="Q81" s="40" t="n">
         <v>9420</v>
       </c>
-      <c r="R80" s="40" t="n">
+      <c r="R81" s="40" t="n">
         <v>6165127</v>
       </c>
-      <c r="S80" s="40" t="n">
+      <c r="S81" s="40" t="n">
         <v>1073449</v>
       </c>
-      <c r="T80" s="40" t="n">
+      <c r="T81" s="40" t="n">
         <v>157.4</v>
       </c>
-      <c r="U80" s="40" t="n">
+      <c r="U81" s="40" t="n">
         <v>113.9</v>
       </c>
     </row>
